--- a/results/Int All Data -0.6/Rando_fi_explain.xlsx
+++ b/results/Int All Data -0.6/Rando_fi_explain.xlsx
@@ -1676,466 +1676,466 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0004945527510077041</v>
+        <v>-0.001020318266600688</v>
       </c>
       <c r="C3" t="n">
-        <v>0.000150171524435201</v>
+        <v>1.529449995973043e-05</v>
       </c>
       <c r="D3" t="n">
-        <v>0.000341530640944756</v>
+        <v>-0.0006470271036667763</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0003834261326471711</v>
+        <v>0.0001495097453580929</v>
       </c>
       <c r="F3" t="n">
-        <v>8.848136198829631e-05</v>
+        <v>-9.749201262520659e-05</v>
       </c>
       <c r="G3" t="n">
-        <v>0.002763873620974875</v>
+        <v>0.0001261435710204961</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0007751810032312966</v>
+        <v>-0.0008311808973852263</v>
       </c>
       <c r="I3" t="n">
-        <v>0.000134405120495642</v>
+        <v>-0.0009656103557739891</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001190076008599209</v>
+        <v>-0.0003236342173417728</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0001498385156808224</v>
+        <v>0.0001798132619040249</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0001091504150075029</v>
+        <v>-0.0001633906036469191</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0005066521583331574</v>
+        <v>-0.0005694833191818981</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0009037352358390726</v>
+        <v>0.0007463607121965376</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.0007273534724962893</v>
+        <v>-0.001805288464419952</v>
       </c>
       <c r="P3" t="n">
-        <v>0.0002387749597115707</v>
+        <v>-0.0003257714240412201</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.005207038135197436</v>
+        <v>0.003611684119892743</v>
       </c>
       <c r="R3" t="n">
-        <v>0.0008872073102919487</v>
+        <v>-0.0001390194041347214</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0001666983211059824</v>
+        <v>-0.001186110457819556</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0001330771872570524</v>
+        <v>-6.632306619634947e-06</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0006475433725749791</v>
+        <v>0.0006735828637247441</v>
       </c>
       <c r="V3" t="n">
-        <v>0.00026799881739895</v>
+        <v>-0.002383339560734706</v>
       </c>
       <c r="W3" t="n">
-        <v>0.00109135592605916</v>
+        <v>0.0009875017141226562</v>
       </c>
       <c r="X3" t="n">
-        <v>0.0006131382801693921</v>
+        <v>0.002202543625804487</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.0004003030714163257</v>
+        <v>0.0001632002366364127</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.0004259387658985591</v>
+        <v>0.0005012721602261584</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.003433404601899701</v>
+        <v>0.003399735685799978</v>
       </c>
       <c r="AB3" t="n">
-        <v>2.233556531499036e-06</v>
+        <v>-0.0006367644530432271</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.001212961502327874</v>
+        <v>-0.001080244214253119</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.004707123292288362</v>
+        <v>0.003374666737402232</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.00688918216938514</v>
+        <v>0.005758267193363071</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.001724991238183229</v>
+        <v>0.0008947519715816332</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0008469977460935085</v>
+        <v>6.932695155273719e-05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.0001301841027068585</v>
+        <v>0.0004479636684480404</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.0008707578843220965</v>
+        <v>0.0006285226465992489</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.002859694426299736</v>
+        <v>0.002402310691112913</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.01312801617557465</v>
+        <v>0.01391307171896165</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.0009942668129819612</v>
+        <v>1.101419586913679e-05</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.003596623152564525</v>
+        <v>0.002121693154699004</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.0008496889818380794</v>
+        <v>-0.0001038028144394077</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.001538717924391426</v>
+        <v>0.001124815604827192</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.0005570605121180473</v>
+        <v>-0.000281533379509885</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.0005579929049250263</v>
+        <v>0.001960924390827646</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.00797310677914433</v>
+        <v>0.004713992115704657</v>
       </c>
       <c r="AS3" t="n">
-        <v>-0.0001345820163995704</v>
+        <v>-0.0003679258479575676</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0.000195179691145626</v>
+        <v>-0.0001726153699882826</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.0003180724453100714</v>
+        <v>0.0004183198476287896</v>
       </c>
       <c r="AV3" t="n">
-        <v>-0.0003217094013634214</v>
+        <v>-0.001304275850223546</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.0008789760740204632</v>
+        <v>-0.001303991996133561</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.0001083700849280355</v>
+        <v>-0.0001668506274152848</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.001800027959642113</v>
+        <v>0.0005847500280487782</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.001456405469006421</v>
+        <v>-0.0005384216599130787</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.004116564271023545</v>
+        <v>0.001435642952088855</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.002791813053101735</v>
+        <v>0.002964591486404592</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0002524717551931987</v>
+        <v>-0.0001878366310690904</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.0001166141768617402</v>
+        <v>-4.578284033295969e-05</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0006644691933226931</v>
+        <v>-0.000359651251267089</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.001621671860763884</v>
+        <v>0.001079972191204226</v>
       </c>
       <c r="BG3" t="n">
-        <v>-6.247009519714681e-05</v>
+        <v>-0.001643306831341489</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0004054300361320094</v>
+        <v>-0.0003314350621181484</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.006965993017147553</v>
+        <v>0.006459402165537649</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0008749144163974487</v>
+        <v>-0.0003098051645940369</v>
       </c>
       <c r="BK3" t="n">
-        <v>-5.10347003058857e-06</v>
+        <v>0.0004022805661006701</v>
       </c>
       <c r="BL3" t="n">
-        <v>-0.000139904161302673</v>
+        <v>0.000130837282314763</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.001008631931100987</v>
+        <v>5.323127571721599e-05</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0028851024518891</v>
+        <v>0.001318169121497417</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.001287255906594377</v>
+        <v>0.0002492710352035643</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.0006487859084545632</v>
+        <v>-0.001029488827939205</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.001635290002767325</v>
+        <v>0.001006880531109175</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.001061586087494593</v>
+        <v>-0.0004837175329135811</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.0008839570656757233</v>
+        <v>9.998721317236781e-05</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.0006537189449160985</v>
+        <v>0.0003585085026919433</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.001001445640857523</v>
+        <v>-0.000411014551045773</v>
       </c>
       <c r="BW3" t="n">
-        <v>-3.106758844292346e-06</v>
+        <v>-1.891522016993164e-05</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.0002960002316662081</v>
+        <v>-0.0006970426806355856</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.0008189126907206624</v>
+        <v>-0.0001222058357904765</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.000757642723928088</v>
+        <v>0.0007890430880278675</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0.0001812914376330121</v>
+        <v>-0.000246974344813361</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.0002178266115868352</v>
+        <v>0.0001614256792341362</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.0009285079366890003</v>
+        <v>0.0004705054047907698</v>
       </c>
       <c r="CD3" t="n">
-        <v>-0.0001541937204086674</v>
+        <v>7.519183879047767e-06</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0.0007744989454878925</v>
+        <v>0.0002820369117247979</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.0004382113581480929</v>
+        <v>-0.000552475699353302</v>
       </c>
       <c r="CG3" t="n">
-        <v>-0.0001587153554445697</v>
+        <v>-0.0001294328755999918</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.0005391811549956504</v>
+        <v>-0.0009494820130947137</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.0001753306203031213</v>
+        <v>-0.0001772267787851978</v>
       </c>
       <c r="CJ3" t="n">
-        <v>-1.57694132322917e-06</v>
+        <v>2.148073443970055e-05</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0.0002285264086624616</v>
+        <v>-0.0001704092689937431</v>
       </c>
       <c r="CL3" t="n">
-        <v>-0.0008499019345865043</v>
+        <v>-0.001534242320394283</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.001125141683303995</v>
+        <v>0.00114562489011421</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.001293381610072729</v>
+        <v>0.001028013467020216</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.0004699390110627077</v>
+        <v>0.0005299860578851067</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.0001788148833466274</v>
+        <v>-0.0002123273951727189</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.001359210078762079</v>
+        <v>0.0003832406056689598</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.001141061438140362</v>
+        <v>-0.0005462846541994071</v>
       </c>
       <c r="CS3" t="n">
-        <v>-0.001853288468157914</v>
+        <v>-0.0007121004627254913</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0.001404609716022591</v>
+        <v>-0.002026979927666993</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.0001014565959581326</v>
+        <v>-3.006547798859783e-05</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.0002112880097871439</v>
+        <v>-3.64687768936811e-05</v>
       </c>
       <c r="CW3" t="n">
         <v>0</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.002670991369881215</v>
+        <v>-0.001462576488985292</v>
       </c>
       <c r="CY3" t="n">
-        <v>-5.680800505641027e-05</v>
+        <v>0.0002360142773688944</v>
       </c>
       <c r="CZ3" t="n">
-        <v>3.896818950187563e-06</v>
+        <v>0.0003456059670789768</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.0003823526938365184</v>
+        <v>8.237297731181535e-05</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.001237897491164623</v>
+        <v>0.0003791387314908756</v>
       </c>
       <c r="DC3" t="n">
-        <v>-0.001875436013320598</v>
+        <v>-0.002203585414686439</v>
       </c>
       <c r="DD3" t="n">
-        <v>6.364090590428307e-05</v>
+        <v>-4.157682298640997e-05</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.001433424803160895</v>
+        <v>0.001161786765397002</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0.0006901775675940216</v>
+        <v>-0.002500254615863268</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.0007969161486549414</v>
+        <v>8.181457850207517e-05</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.001230079013835934</v>
+        <v>-5.268774330672203e-05</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.0003238986141046829</v>
+        <v>-0.0004946138170178316</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.001135427629057418</v>
+        <v>-4.686531826634251e-05</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.0003344968804248971</v>
+        <v>-0.001519169659258609</v>
       </c>
       <c r="DL3" t="n">
-        <v>6.237356007969709e-05</v>
+        <v>-5.938929551867587e-05</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0.001009972836246347</v>
+        <v>-1.54885285228779e-05</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.0002630124449209293</v>
+        <v>-0.0003024287462303777</v>
       </c>
       <c r="DO3" t="n">
-        <v>-0.001652066603990982</v>
+        <v>-0.002997395854852076</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0.002870681151662696</v>
+        <v>-0.001192038535621426</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.0001328564588800285</v>
+        <v>6.241547052765361e-05</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.0001068158106823014</v>
+        <v>8.669144515078941e-05</v>
       </c>
       <c r="DS3" t="n">
-        <v>-0.000317947763295211</v>
+        <v>-4.403186640603018e-05</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0.00032460507146993</v>
+        <v>-0.001321872294623106</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0.000592312569013973</v>
+        <v>-0.0008093221498273885</v>
       </c>
       <c r="DV3" t="n">
-        <v>-5.945242967843045e-06</v>
+        <v>-2.959455460196381e-06</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.0002482650740417747</v>
+        <v>0.0002490473591758746</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.0001358682771980957</v>
+        <v>-0.0001803335623987345</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.001062876925880768</v>
+        <v>-5.804223213810803e-05</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0.0001644640107978246</v>
+        <v>9.884573598203938e-05</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.0006718035326797234</v>
+        <v>-0.000823875314087562</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.002058171070031966</v>
+        <v>-0.002150667429340378</v>
       </c>
       <c r="EC3" t="n">
-        <v>-0.0001313320465175471</v>
+        <v>-0.000340633107605407</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.0002803596813021492</v>
+        <v>-6.954666076768203e-05</v>
       </c>
       <c r="EE3" t="n">
-        <v>9.825292739517599e-05</v>
+        <v>8.983711754248058e-05</v>
       </c>
       <c r="EF3" t="n">
-        <v>-0.0009771123613294685</v>
+        <v>-0.0005762565647452323</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0005434940705280399</v>
+        <v>-7.681012746288849e-05</v>
       </c>
       <c r="EH3" t="n">
-        <v>-5.306700096641802e-05</v>
+        <v>-1.300389353892087e-06</v>
       </c>
       <c r="EI3" t="n">
-        <v>-0.0003948271220630717</v>
+        <v>-0.0009472831542672987</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0005484716719482263</v>
+        <v>-0.0006405657031873913</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.0008589311780560039</v>
+        <v>0.0001672018735774727</v>
       </c>
       <c r="EL3" t="n">
-        <v>-4.83764919923102e-05</v>
+        <v>-5.948462180254466e-05</v>
       </c>
       <c r="EM3" t="n">
-        <v>-2.887600448382877e-05</v>
+        <v>1.178681727993069e-05</v>
       </c>
       <c r="EN3" t="n">
-        <v>-1.066637179659602e-05</v>
+        <v>-9.273814924461887e-05</v>
       </c>
       <c r="EO3" t="n">
-        <v>1.184132622853884e-05</v>
+        <v>0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-1.064027453109074e-05</v>
+        <v>0.0001477950367049996</v>
       </c>
       <c r="EQ3" t="n">
-        <v>-6.721093794102796e-05</v>
+        <v>-0.00039290062420408</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0.0002803044559962985</v>
+        <v>-7.855453455801186e-05</v>
       </c>
       <c r="ES3" t="n">
-        <v>9.769868525718261e-05</v>
+        <v>-0.0001650374906745411</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.001236240292475245</v>
+        <v>-0.0001999403361952124</v>
       </c>
       <c r="EU3" t="n">
-        <v>-0.0009571701923004262</v>
+        <v>-0.0005576796046930765</v>
       </c>
       <c r="EV3" t="n">
-        <v>8.242677261913523e-05</v>
+        <v>-0.0001654781736427713</v>
       </c>
       <c r="EW3" t="n">
-        <v>-0.0003271240644661411</v>
+        <v>-0.0009411694007368709</v>
       </c>
       <c r="EX3" t="n">
-        <v>6.316562051082554e-05</v>
+        <v>-0.0008146282235933765</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.0002126488917827929</v>
+        <v>0.0001768175431916485</v>
       </c>
     </row>
     <row r="4">
@@ -2145,466 +2145,466 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.002495017812811049</v>
+        <v>0.005248241703206677</v>
       </c>
       <c r="C4" t="n">
-        <v>0.002055267700526713</v>
+        <v>0.001997264163811904</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001189628352759865</v>
+        <v>0.0009378439390599636</v>
       </c>
       <c r="E4" t="n">
-        <v>0.001161788416144809</v>
+        <v>0.0008324592160606914</v>
       </c>
       <c r="F4" t="n">
-        <v>0.001280739314089612</v>
+        <v>0.001174895599556651</v>
       </c>
       <c r="G4" t="n">
-        <v>0.003067599871546771</v>
+        <v>0.001679648206258714</v>
       </c>
       <c r="H4" t="n">
-        <v>0.001417004282922946</v>
+        <v>0.001789468210881712</v>
       </c>
       <c r="I4" t="n">
-        <v>0.002796007080626607</v>
+        <v>0.003810844702483728</v>
       </c>
       <c r="J4" t="n">
-        <v>0.00239196873584298</v>
+        <v>0.00186407429152846</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0008828545319890276</v>
+        <v>0.0006506428608420918</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0005539778696899201</v>
+        <v>0.0008360276690987512</v>
       </c>
       <c r="M4" t="n">
-        <v>0.001770847390132818</v>
+        <v>0.001979029516838137</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0066162575713693</v>
+        <v>0.005300778537409137</v>
       </c>
       <c r="O4" t="n">
-        <v>0.003142878045113227</v>
+        <v>0.004152113315928021</v>
       </c>
       <c r="P4" t="n">
-        <v>0.001108780252932833</v>
+        <v>0.00117378748186448</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.008365227944168377</v>
+        <v>0.006367993743558742</v>
       </c>
       <c r="R4" t="n">
-        <v>0.001445996915406969</v>
+        <v>0.002109671726114202</v>
       </c>
       <c r="S4" t="n">
-        <v>0.00266952029237774</v>
+        <v>0.003574608168006696</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0007311340192401414</v>
+        <v>0.001237437230199322</v>
       </c>
       <c r="U4" t="n">
-        <v>0.001875291949898297</v>
+        <v>0.0009481118882426561</v>
       </c>
       <c r="V4" t="n">
-        <v>0.002989364550135872</v>
+        <v>0.006776454935975295</v>
       </c>
       <c r="W4" t="n">
-        <v>0.001653938939875728</v>
+        <v>0.00224300870609748</v>
       </c>
       <c r="X4" t="n">
-        <v>0.004975379733423434</v>
+        <v>0.005066361159908389</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.0007039110386706972</v>
+        <v>0.0003200758235453937</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.004908282623226724</v>
+        <v>0.00434275201606149</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.008957915452645231</v>
+        <v>0.006534878522211692</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.0007776863389826488</v>
+        <v>0.001484648520240874</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.002333976401853565</v>
+        <v>0.001025034907819945</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.006131025925925987</v>
+        <v>0.005680123320391595</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.007093200191558661</v>
+        <v>0.007177087743550528</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.002662034989981116</v>
+        <v>0.003056403967155031</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.001169185612729595</v>
+        <v>0.00242335280590995</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.0009743747888587255</v>
+        <v>0.002280335720875964</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.002767531725581373</v>
+        <v>0.00315914613506115</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.004983173940781131</v>
+        <v>0.002340639426774705</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.008905080409051254</v>
+        <v>0.01224651006203716</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.003097927650072997</v>
+        <v>0.001763996567404197</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.006181652551156052</v>
+        <v>0.006049183929612675</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.004242219953996756</v>
+        <v>0.003546256218838801</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.004289239018080584</v>
+        <v>0.005553592392558545</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.001616988678058763</v>
+        <v>0.001615625250271114</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.004693026334765268</v>
+        <v>0.003162151484633011</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.005501971177452709</v>
+        <v>0.003838233703440989</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.003695055408727363</v>
+        <v>0.003741483924097644</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.004066308931657193</v>
+        <v>0.002093761159728977</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.002016568255911486</v>
+        <v>0.002411261022741944</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.001374062588423678</v>
+        <v>0.002242665447082028</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.002272112677002825</v>
+        <v>0.003230883183034001</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.001390740401751873</v>
+        <v>0.0006056548313519274</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.002446501764605518</v>
+        <v>0.001798978134080061</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.001792781535494176</v>
+        <v>0.00373837825329187</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.005673992834308563</v>
+        <v>0.005847997090479148</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.004689774255775262</v>
+        <v>0.00555001654227065</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0006308728295021216</v>
+        <v>0.0008612369690300099</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.001106200559746449</v>
+        <v>0.0006000701168996006</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.001882413810211501</v>
+        <v>0.001738635329996893</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.005471123579381957</v>
+        <v>0.007059329456299125</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.002398149375336094</v>
+        <v>0.004364199673848393</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.001137920548927858</v>
+        <v>0.002224834960342685</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.008359701243760075</v>
+        <v>0.01255109282316419</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.002793711641490706</v>
+        <v>0.001719200487207089</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.003113369122974428</v>
+        <v>0.003016483303259963</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0009777403727268819</v>
+        <v>0.0007273966802439409</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.001539831090063729</v>
+        <v>0.001609154078911263</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.005268826143038936</v>
+        <v>0.003208533993086737</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.004107163394834776</v>
+        <v>0.002835066139085318</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.00159022904351262</v>
+        <v>0.001667285874669666</v>
       </c>
       <c r="BQ4" t="n">
         <v>0</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.004139764289540829</v>
+        <v>0.003192264506209193</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.002016786047077475</v>
+        <v>0.001863964378567626</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.0009683663873239052</v>
+        <v>0.001747709830950652</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.003471276747806333</v>
+        <v>0.001642004264740927</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.001886263822342812</v>
+        <v>0.00149303750288909</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.505054999733844e-05</v>
+        <v>0.0001503832657674169</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.001862813570299144</v>
+        <v>0.001404445690796605</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.003223201152597032</v>
+        <v>0.002929312817866152</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.002635631649958222</v>
+        <v>0.001851243543680843</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.001273894648218828</v>
+        <v>0.001312174387993084</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.003079347701538142</v>
+        <v>0.001335081282573999</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.002408776885092149</v>
+        <v>0.001544170076762245</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.001394345635544508</v>
+        <v>0.00201697556449537</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.003997785569850515</v>
+        <v>0.004096316521028942</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.001397181355866044</v>
+        <v>0.0009388950792281108</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.001495684161735096</v>
+        <v>0.0008378260410384779</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.001117244482469852</v>
+        <v>0.001566832948865884</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.001538334451978504</v>
+        <v>0.001245234071701778</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.0001258533088214575</v>
+        <v>0.0001170691191596647</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.002046581747830183</v>
+        <v>0.001678569002981546</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.003874907074244098</v>
+        <v>0.004242732494086963</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.002218181444912776</v>
+        <v>0.001748982904083944</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.002303824526859374</v>
+        <v>0.0009381277592484843</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.001928314813500798</v>
+        <v>0.002878708434350524</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.0003190470755502309</v>
+        <v>0.0002203287530496638</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.003367243580543723</v>
+        <v>0.003872564573550514</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.003705116714606071</v>
+        <v>0.005452633359389596</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.003768444302046071</v>
+        <v>0.002305195230007985</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.003378927039283367</v>
+        <v>0.003681392521343235</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.0005315497580388891</v>
+        <v>0.0002852571365103981</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.0003643954698812741</v>
+        <v>0.0002855031719468898</v>
       </c>
       <c r="CW4" t="n">
         <v>0</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.005348871222795145</v>
+        <v>0.003845637820753216</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.00325381546027095</v>
+        <v>0.003299806889518284</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.000427272683301536</v>
+        <v>0.0007918426689987288</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.000590692872237918</v>
+        <v>0.0005804044149527843</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.001610263390202788</v>
+        <v>0.001850926584289635</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.002706249550770076</v>
+        <v>0.005678596309303718</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.0004340988629852153</v>
+        <v>0.0004213616055862111</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.002066761798914036</v>
+        <v>0.002432005972583114</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.003887067704467621</v>
+        <v>0.007215205750559031</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.002142363158339066</v>
+        <v>0.001168572214433919</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.005943922633301756</v>
+        <v>0.004708826167928204</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.001678334970765905</v>
+        <v>0.002436122909022572</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.003631241568634224</v>
+        <v>0.001551255237629487</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.002692696650095528</v>
+        <v>0.006368991365113872</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.0001590580296906046</v>
+        <v>0.00074076262708784</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.001453379088741948</v>
+        <v>0.001672634757840963</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.005008102411987504</v>
+        <v>0.00374506816196173</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.004490436829636102</v>
+        <v>0.003705991804026119</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.005266652333413654</v>
+        <v>0.003330151605978187</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.0006858945234479739</v>
+        <v>0.0003058628504538376</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0002931054664694471</v>
+        <v>0.0002171531326577016</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.0006951874871680467</v>
+        <v>9.647579463734613e-05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.004218413818401761</v>
+        <v>0.00279786559995587</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.002969270301957123</v>
+        <v>0.002876340069184876</v>
       </c>
       <c r="DV4" t="n">
-        <v>3.05539728721408e-05</v>
+        <v>9.358619888042345e-06</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.000600194511732687</v>
+        <v>0.0005400308334745791</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.001573763940736855</v>
+        <v>0.001314941143561703</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.004880800139563193</v>
+        <v>0.004820528649926734</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.0004506295853943746</v>
+        <v>0.000620773876451083</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.002874695666240667</v>
+        <v>0.003237889502227309</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.004142130166780974</v>
+        <v>0.00448733334177269</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.00229695576820115</v>
+        <v>0.001423352440303415</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.001519063859733202</v>
+        <v>0.0008954327415968361</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.0001154162844406381</v>
+        <v>0.0001241541255340752</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.001879172490616517</v>
+        <v>0.001784086493180896</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.001110531940768553</v>
+        <v>0.0006858856959528635</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.0006747008581061606</v>
+        <v>0.0003874314175663494</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.002548136919427356</v>
+        <v>0.002015353779334917</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.001160352602362997</v>
+        <v>0.00158019138422589</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.001495895700675586</v>
+        <v>0.002090041388558147</v>
       </c>
       <c r="EL4" t="n">
-        <v>8.91217651875604e-05</v>
+        <v>0.000153236990291833</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.0002593962555123788</v>
+        <v>0.0003739735983355897</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.0004324342601337662</v>
+        <v>0.0004785721270039804</v>
       </c>
       <c r="EO4" t="n">
-        <v>3.744556139927426e-05</v>
+        <v>0</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.0007487787251994056</v>
+        <v>0.0004759793979735452</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.001116304976635158</v>
+        <v>0.0008571019528754811</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.0008887475817805922</v>
+        <v>0.0002955755036644011</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.0002426791543904409</v>
+        <v>0.0003851929595862845</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.00144664686351874</v>
+        <v>0.001286677276352757</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.002605266037519087</v>
+        <v>0.001972782987411346</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.0003027568604996876</v>
+        <v>0.0004732892500432981</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.0007526576076561637</v>
+        <v>0.002467962270134412</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.0015291819193307</v>
+        <v>0.001451146096590292</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.001007027951855403</v>
+        <v>0.0009547838569450625</v>
       </c>
     </row>
     <row r="5">
@@ -2614,466 +2614,466 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.003453545232273825</v>
+        <v>-0.01253056234718829</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.004997025580011938</v>
+        <v>-0.004828850855745748</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.002298850574712586</v>
+        <v>-0.002416740347774859</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.001272565847883966</v>
+        <v>-0.001283618581907131</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.001798879386611663</v>
+        <v>-0.002320047590719765</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.002218380870066239</v>
+        <v>-0.002652106084243422</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.001887348864641736</v>
+        <v>-0.003056234718826434</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.005157677571470643</v>
+        <v>-0.008160146699266523</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.001592450604541484</v>
+        <v>-0.003539559785841728</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.001503094606542843</v>
+        <v>-0.001065975223278604</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0005010315355142402</v>
+        <v>-0.001653666146645905</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.003169115528666067</v>
+        <v>-0.005070584845865755</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.009766637856525474</v>
+        <v>-0.008268330733229357</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.007304400977995074</v>
+        <v>-0.01274449877750613</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.001945181255526029</v>
+        <v>-0.002215288611544508</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.009814323607427001</v>
+        <v>-0.007161803713527881</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.001238572692421147</v>
+        <v>-0.004309290953545253</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.003975799481417441</v>
+        <v>-0.006770383174877581</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0006794682422451958</v>
+        <v>-0.001606186793575204</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.003331350386674625</v>
+        <v>-0.0007077558242406413</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.005348410757946198</v>
+        <v>-0.01512836185819073</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.0009473060982830072</v>
+        <v>-0.002964118564742635</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.008863771564544931</v>
+        <v>-0.006097560975609739</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0005624629958555283</v>
+        <v>-0.0003538779121203373</v>
       </c>
       <c r="Z5" t="n">
-        <v>-0.007753773305711776</v>
+        <v>-0.007721780135573264</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.004011281729865257</v>
+        <v>-0.001503981126511378</v>
       </c>
       <c r="AB5" t="n">
-        <v>-0.001754935756816067</v>
+        <v>-0.003361858190709077</v>
       </c>
       <c r="AC5" t="n">
-        <v>-0.002623047450633609</v>
+        <v>-0.002506635210852293</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.006885623739556301</v>
+        <v>-0.006338231057332189</v>
       </c>
       <c r="AE5" t="n">
-        <v>0.0001880288310874057</v>
+        <v>-0.002182247124741998</v>
       </c>
       <c r="AF5" t="n">
-        <v>-0.001620984379605028</v>
+        <v>-0.005287286063569707</v>
       </c>
       <c r="AG5" t="n">
-        <v>-0.001065975223278559</v>
+        <v>-0.003619344773790989</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.001041046995835848</v>
+        <v>-0.004898595943837803</v>
       </c>
       <c r="AI5" t="n">
-        <v>-0.002534630120836956</v>
+        <v>-0.005210608424337004</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.006142275148856157</v>
+        <v>-0.001161369193154049</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.002103140305387485</v>
+        <v>-0.004206280610774993</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.002260559190957789</v>
+        <v>-0.001716484166913368</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.007726334414627012</v>
+        <v>-0.003125921557062838</v>
       </c>
       <c r="AN5" t="n">
-        <v>-0.00615748963883953</v>
+        <v>-0.004552002304811309</v>
       </c>
       <c r="AO5" t="n">
-        <v>-0.002141582391433705</v>
+        <v>-0.00547066014669928</v>
       </c>
       <c r="AP5" t="n">
-        <v>-0.001670988187842093</v>
+        <v>-0.003681747269890834</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.005073349633251812</v>
+        <v>-0.003745207903273407</v>
       </c>
       <c r="AR5" t="n">
-        <v>-0.004439183190293006</v>
+        <v>-0.003636919315403464</v>
       </c>
       <c r="AS5" t="n">
-        <v>-0.002574726250369952</v>
+        <v>-0.006107749927974637</v>
       </c>
       <c r="AT5" t="n">
-        <v>-0.005570291777188296</v>
+        <v>-0.003276131045241859</v>
       </c>
       <c r="AU5" t="n">
-        <v>-0.001620984379605017</v>
+        <v>-0.003093396787626368</v>
       </c>
       <c r="AV5" t="n">
-        <v>-0.002328323017978151</v>
+        <v>-0.005264723378941061</v>
       </c>
       <c r="AW5" t="n">
-        <v>-0.004370415647921744</v>
+        <v>-0.007457212713936456</v>
       </c>
       <c r="AX5" t="n">
-        <v>-0.002371294851794126</v>
+        <v>-0.001011302795954738</v>
       </c>
       <c r="AY5" t="n">
-        <v>-0.001326259946949537</v>
+        <v>-0.001185647425897085</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.0009815585960737728</v>
+        <v>-0.007854523227383892</v>
       </c>
       <c r="BA5" t="n">
-        <v>-0.002652106084243433</v>
+        <v>-0.007550702028081169</v>
       </c>
       <c r="BB5" t="n">
-        <v>-0.00746092598053677</v>
+        <v>-0.002059282371294901</v>
       </c>
       <c r="BC5" t="n">
-        <v>-0.0009431181844974379</v>
+        <v>-0.001560062402496143</v>
       </c>
       <c r="BD5" t="n">
-        <v>-0.003153551429413448</v>
+        <v>-0.001404056162246547</v>
       </c>
       <c r="BE5" t="n">
-        <v>-0.002679343128781308</v>
+        <v>-0.003313166234514542</v>
       </c>
       <c r="BF5" t="n">
-        <v>-0.007675507020280858</v>
+        <v>-0.006222353288115634</v>
       </c>
       <c r="BG5" t="n">
-        <v>-0.004737163814180911</v>
+        <v>-0.01216381418092915</v>
       </c>
       <c r="BH5" t="n">
-        <v>-0.001267315060418473</v>
+        <v>-0.004461629982153459</v>
       </c>
       <c r="BI5" t="n">
-        <v>-0.001002063071028525</v>
+        <v>-0.005190209377764698</v>
       </c>
       <c r="BJ5" t="n">
-        <v>-0.003332350339133039</v>
+        <v>-0.002839313572542956</v>
       </c>
       <c r="BK5" t="n">
-        <v>-0.005837408312958414</v>
+        <v>-0.004767726161369223</v>
       </c>
       <c r="BL5" t="n">
-        <v>-0.001963117192147556</v>
+        <v>-0.0009795447997695272</v>
       </c>
       <c r="BM5" t="n">
-        <v>-0.001959089599539021</v>
+        <v>-0.002161042036708116</v>
       </c>
       <c r="BN5" t="n">
-        <v>-0.003373779224622686</v>
+        <v>-0.002383863080684612</v>
       </c>
       <c r="BO5" t="n">
-        <v>-0.003048239124001228</v>
+        <v>-0.003931357254290213</v>
       </c>
       <c r="BP5" t="n">
-        <v>-0.002663741773738648</v>
+        <v>-0.004024960998439952</v>
       </c>
       <c r="BQ5" t="n">
         <v>0</v>
       </c>
       <c r="BR5" t="n">
-        <v>-0.004180967238689581</v>
+        <v>-0.003588143525741072</v>
       </c>
       <c r="BS5" t="n">
-        <v>-0.001945181255526029</v>
+        <v>-0.004174067495559519</v>
       </c>
       <c r="BT5" t="n">
-        <v>-0.0006782659982306316</v>
+        <v>-0.002498512790005924</v>
       </c>
       <c r="BU5" t="n">
-        <v>-0.006015924506045456</v>
+        <v>-0.002371294851794092</v>
       </c>
       <c r="BV5" t="n">
-        <v>-0.002535292422932856</v>
+        <v>-0.004033419763756841</v>
       </c>
       <c r="BW5" t="n">
-        <v>-0.0002367564368156216</v>
+        <v>-0.0003271861986912317</v>
       </c>
       <c r="BX5" t="n">
-        <v>-0.002820432466311517</v>
+        <v>-0.003453545232273869</v>
       </c>
       <c r="BY5" t="n">
-        <v>-0.004541433205544132</v>
+        <v>-0.006479217603912002</v>
       </c>
       <c r="BZ5" t="n">
-        <v>-0.00263240363522409</v>
+        <v>-0.001598579040852588</v>
       </c>
       <c r="CA5" t="n">
-        <v>-0.001754907792980398</v>
+        <v>-0.001584557764333061</v>
       </c>
       <c r="CB5" t="n">
-        <v>-0.003169115528666067</v>
+        <v>-0.002152886115444663</v>
       </c>
       <c r="CC5" t="n">
-        <v>-0.001974302726418054</v>
+        <v>-0.002621722846441954</v>
       </c>
       <c r="CD5" t="n">
-        <v>-0.003242117787031562</v>
+        <v>-0.003663220088626273</v>
       </c>
       <c r="CE5" t="n">
-        <v>-0.005647425897035918</v>
+        <v>-0.003716508210890235</v>
       </c>
       <c r="CF5" t="n">
-        <v>-0.001798879386611652</v>
+        <v>-0.001778471138845594</v>
       </c>
       <c r="CG5" t="n">
-        <v>-0.002938634399308537</v>
+        <v>-0.001864303178484161</v>
       </c>
       <c r="CH5" t="n">
-        <v>-0.001474491300501368</v>
+        <v>-0.003197925669835777</v>
       </c>
       <c r="CI5" t="n">
-        <v>-0.002016709881878409</v>
+        <v>-0.002074330164217819</v>
       </c>
       <c r="CJ5" t="n">
-        <v>-0.000267697798929234</v>
+        <v>-0.0002960331557134599</v>
       </c>
       <c r="CK5" t="n">
-        <v>-0.004883101509322307</v>
+        <v>-0.003775351014040596</v>
       </c>
       <c r="CL5" t="n">
-        <v>-0.008644168146832443</v>
+        <v>-0.0133214920071048</v>
       </c>
       <c r="CM5" t="n">
-        <v>-0.001100535395597879</v>
+        <v>-0.001670988187842115</v>
       </c>
       <c r="CN5" t="n">
-        <v>-0.001354076634975487</v>
+        <v>-2.881014116971059e-05</v>
       </c>
       <c r="CO5" t="n">
-        <v>-0.00414323764427349</v>
+        <v>-0.004461629982153459</v>
       </c>
       <c r="CP5" t="n">
-        <v>-0.0001440507058484419</v>
+        <v>-0.000531757754800588</v>
       </c>
       <c r="CQ5" t="n">
-        <v>-0.003965670316661762</v>
+        <v>-0.006836342113051275</v>
       </c>
       <c r="CR5" t="n">
-        <v>-0.009650680876258134</v>
+        <v>-0.01417998815867376</v>
       </c>
       <c r="CS5" t="n">
-        <v>-0.009739490822972163</v>
+        <v>-0.006779159265837808</v>
       </c>
       <c r="CT5" t="n">
-        <v>-0.00746003552397867</v>
+        <v>-0.009413854351687401</v>
       </c>
       <c r="CU5" t="n">
-        <v>-0.0003848431024274679</v>
+        <v>-0.0004439183190293572</v>
       </c>
       <c r="CV5" t="n">
-        <v>-0.0002820432466311251</v>
+        <v>-0.0004889975550122827</v>
       </c>
       <c r="CW5" t="n">
         <v>0</v>
       </c>
       <c r="CX5" t="n">
-        <v>-0.013299911530522</v>
+        <v>-0.01083481349911192</v>
       </c>
       <c r="CY5" t="n">
-        <v>-0.007933688573120179</v>
+        <v>-0.006483126110124337</v>
       </c>
       <c r="CZ5" t="n">
-        <v>-0.0009474327628361756</v>
+        <v>-0.0004164187983342948</v>
       </c>
       <c r="DA5" t="n">
-        <v>-0.0003538779121203484</v>
+        <v>-0.0006778661951076126</v>
       </c>
       <c r="DB5" t="n">
-        <v>-0.001924215512137339</v>
+        <v>-0.002825698988697167</v>
       </c>
       <c r="DC5" t="n">
-        <v>-0.00657623120023596</v>
+        <v>-0.01764357608052102</v>
       </c>
       <c r="DD5" t="n">
-        <v>-0.001061007957559612</v>
+        <v>-0.0007488299531981602</v>
       </c>
       <c r="DE5" t="n">
-        <v>-0.00192364604912697</v>
+        <v>-0.003301606186793526</v>
       </c>
       <c r="DF5" t="n">
-        <v>-0.01104203670811131</v>
+        <v>-0.02164002368265249</v>
       </c>
       <c r="DG5" t="n">
-        <v>-0.001959089599539032</v>
+        <v>-0.002141582391433627</v>
       </c>
       <c r="DH5" t="n">
-        <v>-0.01014277215942895</v>
+        <v>-0.005264723378941083</v>
       </c>
       <c r="DI5" t="n">
-        <v>-0.003140305387496378</v>
+        <v>-0.006482281763180653</v>
       </c>
       <c r="DJ5" t="n">
-        <v>-0.01105216622457996</v>
+        <v>-0.003183023872679081</v>
       </c>
       <c r="DK5" t="n">
-        <v>-0.005806071323312656</v>
+        <v>-0.0187739463601533</v>
       </c>
       <c r="DL5" t="n">
-        <v>-0.0001189767995240842</v>
+        <v>-0.002022605591909554</v>
       </c>
       <c r="DM5" t="n">
-        <v>-0.004155614500442051</v>
+        <v>-0.003450327186198665</v>
       </c>
       <c r="DN5" t="n">
-        <v>-0.005809495723975255</v>
+        <v>-0.006424747174300982</v>
       </c>
       <c r="DO5" t="n">
-        <v>-0.0111243307555027</v>
+        <v>-0.009739490822972175</v>
       </c>
       <c r="DP5" t="n">
-        <v>-0.01332540154669842</v>
+        <v>-0.009220701963117139</v>
       </c>
       <c r="DQ5" t="n">
-        <v>-0.001629583202757756</v>
+        <v>-0.0005928237129485426</v>
       </c>
       <c r="DR5" t="n">
-        <v>-0.0003847292098253851</v>
+        <v>-0.0001179593040401383</v>
       </c>
       <c r="DS5" t="n">
-        <v>-0.002101835405565433</v>
+        <v>-0.0002304811293575404</v>
       </c>
       <c r="DT5" t="n">
-        <v>-0.007436049970255832</v>
+        <v>-0.008060678167757251</v>
       </c>
       <c r="DU5" t="n">
-        <v>-0.006867969212551795</v>
+        <v>-0.0061870929544109</v>
       </c>
       <c r="DV5" t="n">
-        <v>-5.918910920390541e-05</v>
+        <v>-2.959455460196381e-05</v>
       </c>
       <c r="DW5" t="n">
-        <v>-0.0004736530491415092</v>
+        <v>-0.0005056513979773469</v>
       </c>
       <c r="DX5" t="n">
-        <v>-0.002538389219680381</v>
+        <v>-0.002074330164217808</v>
       </c>
       <c r="DY5" t="n">
-        <v>-0.01183819155264725</v>
+        <v>-0.01136228435455081</v>
       </c>
       <c r="DZ5" t="n">
-        <v>-0.001031535514294091</v>
+        <v>-0.0009795447997695272</v>
       </c>
       <c r="EA5" t="n">
-        <v>-0.006100795755968125</v>
+        <v>-0.009902740937223741</v>
       </c>
       <c r="EB5" t="n">
-        <v>-0.01115407495538374</v>
+        <v>-0.01038072575847706</v>
       </c>
       <c r="EC5" t="n">
-        <v>-0.003892657033323543</v>
+        <v>-0.004033419763756841</v>
       </c>
       <c r="ED5" t="n">
-        <v>-0.001620984379605006</v>
+        <v>-0.001532567049808464</v>
       </c>
       <c r="EE5" t="n">
-        <v>0</v>
+        <v>-0.0001728608470181303</v>
       </c>
       <c r="EF5" t="n">
-        <v>-0.00598290598290595</v>
+        <v>-0.003820293398533026</v>
       </c>
       <c r="EG5" t="n">
-        <v>-0.00221838087006625</v>
+        <v>-0.001190849263553784</v>
       </c>
       <c r="EH5" t="n">
-        <v>-0.001657295057709351</v>
+        <v>-0.0005624629958555505</v>
       </c>
       <c r="EI5" t="n">
-        <v>-0.006778661951075715</v>
+        <v>-0.005599764220453896</v>
       </c>
       <c r="EJ5" t="n">
-        <v>-0.00318302387267898</v>
+        <v>-0.003284356093344876</v>
       </c>
       <c r="EK5" t="n">
-        <v>-0.004273504273504236</v>
+        <v>-0.004951370468611882</v>
       </c>
       <c r="EL5" t="n">
-        <v>-0.0002367564368156216</v>
+        <v>-0.0004126142057176985</v>
       </c>
       <c r="EM5" t="n">
-        <v>-0.0006189213085764145</v>
+        <v>-0.0007398638650489176</v>
       </c>
       <c r="EN5" t="n">
-        <v>-0.0005612998522895096</v>
+        <v>-0.0009360374414976724</v>
       </c>
       <c r="EO5" t="n">
         <v>0</v>
       </c>
       <c r="EP5" t="n">
-        <v>-0.0008147916013788947</v>
+        <v>-0.0008643042350907737</v>
       </c>
       <c r="EQ5" t="n">
-        <v>-0.002298850574712596</v>
+        <v>-0.002121684867394746</v>
       </c>
       <c r="ER5" t="n">
-        <v>-0.002799882110226903</v>
+        <v>-0.0008841732979664285</v>
       </c>
       <c r="ES5" t="n">
-        <v>-0.0001477104874446078</v>
+        <v>-0.001189767995240853</v>
       </c>
       <c r="ET5" t="n">
-        <v>-0.004332449160035334</v>
+        <v>-0.002446212791040414</v>
       </c>
       <c r="EU5" t="n">
-        <v>-0.008045977011494209</v>
+        <v>-0.00294724432655471</v>
       </c>
       <c r="EV5" t="n">
-        <v>-0.0002359186080802322</v>
+        <v>-0.00141169691731492</v>
       </c>
       <c r="EW5" t="n">
-        <v>-0.001503094606542843</v>
+        <v>-0.00558916738692018</v>
       </c>
       <c r="EX5" t="n">
-        <v>-0.002505157677571423</v>
+        <v>-0.004244031830238748</v>
       </c>
       <c r="EY5" t="n">
-        <v>-0.001420538620893741</v>
+        <v>-0.001925427872860663</v>
       </c>
     </row>
     <row r="6">
@@ -3083,466 +3083,466 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0005353665085804566</v>
+        <v>-0.001763356355501858</v>
       </c>
       <c r="C6" t="n">
-        <v>-3.561965503186826e-05</v>
+        <v>-0.0007220574772614563</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0003617896430432422</v>
+        <v>-0.001193515959552316</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0004724644739071665</v>
+        <v>-0.0002582454347716173</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0007598129685137456</v>
+        <v>-0.0003977615569038334</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0008059460584992878</v>
+        <v>-0.001166690697027104</v>
       </c>
       <c r="H6" t="n">
-        <v>7.6605178888467e-06</v>
+        <v>-0.002441198091055108</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.001183403414129647</v>
+        <v>-0.002425979797812636</v>
       </c>
       <c r="J6" t="n">
-        <v>-5.598567959454737e-05</v>
+        <v>-0.0014309920575729</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0003822712879998747</v>
+        <v>-0.0001698844741171518</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.0002549215705703794</v>
+        <v>-0.000303377239825639</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0009472425812549201</v>
+        <v>-0.0008273598416658895</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.002702620430609137</v>
+        <v>-0.001836133705215895</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.002145095246246701</v>
+        <v>-0.002647251363532097</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.0002515230507237259</v>
+        <v>-0.001193577655564449</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0001618775195387056</v>
+        <v>-0.001176817232547239</v>
       </c>
       <c r="R6" t="n">
-        <v>-0.0001362214346477986</v>
+        <v>-0.001027906284790758</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.002301521990646435</v>
+        <v>-0.004118073779524145</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0003345165854292703</v>
+        <v>-0.001050394213559544</v>
       </c>
       <c r="U6" t="n">
-        <v>-2.220446049250313e-17</v>
+        <v>-2.340093603745153e-05</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.001101970989274204</v>
+        <v>-0.006270340468791208</v>
       </c>
       <c r="W6" t="n">
-        <v>0.0002046513476192307</v>
+        <v>-0.0005287395813872136</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.0006855993435580438</v>
+        <v>0.0003458797744419012</v>
       </c>
       <c r="Y6" t="n">
-        <v>2.350360388594375e-05</v>
+        <v>7.800312012479216e-06</v>
       </c>
       <c r="Z6" t="n">
-        <v>-0.00196044038263398</v>
+        <v>-0.002682783295203275</v>
       </c>
       <c r="AA6" t="n">
-        <v>-0.003177734005911947</v>
+        <v>-0.0009542519631820261</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0.0001956450730438014</v>
+        <v>-0.001115316729419799</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.0001554042652954723</v>
+        <v>-0.001794566035515041</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.002065655756627796</v>
+        <v>0.0003497078015184812</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.001725442169142655</v>
+        <v>0.0009915358522521788</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.0001059989748653206</v>
+        <v>-0.0004542564499945501</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.513673341722031e-05</v>
+        <v>-0.0007325112214877</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.0006932240601928458</v>
+        <v>0.0002216837596712234</v>
       </c>
       <c r="AI6" t="n">
-        <v>-0.0007648453648633702</v>
+        <v>-0.0003913457239489992</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.0003611605703674664</v>
+        <v>0.0001548998089027643</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.008774174086590461</v>
+        <v>0.004726021241735917</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.0006710768167640019</v>
+        <v>-0.0007167325635596717</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0003173782661184565</v>
+        <v>-0.001878094159528221</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.001456812769533683</v>
+        <v>-0.002384988589571746</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.001548791473625585</v>
+        <v>-0.002863982796259662</v>
       </c>
       <c r="AP6" t="n">
-        <v>-0.0002321695116990929</v>
+        <v>-0.001247437473474056</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0.00240765520516836</v>
+        <v>-0.0002908467889675804</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.006847995518951144</v>
+        <v>0.002660335610385925</v>
       </c>
       <c r="AS6" t="n">
-        <v>-0.002394851916370022</v>
+        <v>-0.003495747997538995</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0.002987536159797502</v>
+        <v>-0.001231726147534787</v>
       </c>
       <c r="AU6" t="n">
-        <v>-0.000872290921041699</v>
+        <v>-0.0007710883211688142</v>
       </c>
       <c r="AV6" t="n">
-        <v>-0.001373334030822881</v>
+        <v>-0.00258548343980409</v>
       </c>
       <c r="AW6" t="n">
-        <v>-0.002416876915570193</v>
+        <v>-0.001984570978238764</v>
       </c>
       <c r="AX6" t="n">
-        <v>-0.0005452749659015544</v>
+        <v>-0.0005032191305929607</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0007213906533789366</v>
+        <v>-0.0004580249472431325</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.0001008338646656643</v>
+        <v>-0.001960957716961678</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0009636774802321391</v>
+        <v>-0.0007920851709484005</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.002007129471328559</v>
+        <v>-0.0009966818664997878</v>
       </c>
       <c r="BC6" t="n">
-        <v>-0.0001182149686849487</v>
+        <v>-0.0009113519885605992</v>
       </c>
       <c r="BD6" t="n">
-        <v>-8.643042350906238e-05</v>
+        <v>-8.491588224266156e-05</v>
       </c>
       <c r="BE6" t="n">
-        <v>-0.0005420270096772178</v>
+        <v>-0.0008148813576737413</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.002287736262540088</v>
+        <v>-0.003177494684106924</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.001016385964701719</v>
+        <v>-0.002464471656331307</v>
       </c>
       <c r="BH6" t="n">
-        <v>-0.0003682125970651762</v>
+        <v>-0.001354129923931527</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.001409419843211676</v>
+        <v>-0.0009919927190815193</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0001047884073135052</v>
+        <v>-0.00163938931554678</v>
       </c>
       <c r="BK6" t="n">
-        <v>-0.001257009288291555</v>
+        <v>-0.001094756408877323</v>
       </c>
       <c r="BL6" t="n">
-        <v>-0.0005988575244608358</v>
+        <v>-0.0004232433959197396</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0002670186736421387</v>
+        <v>-0.001087899564963826</v>
       </c>
       <c r="BN6" t="n">
-        <v>-0.0008446718877307552</v>
+        <v>-0.0006365418450945709</v>
       </c>
       <c r="BO6" t="n">
-        <v>-0.001479511417038201</v>
+        <v>-0.001932440836556743</v>
       </c>
       <c r="BP6" t="n">
-        <v>-0.001765614599787355</v>
+        <v>-0.001603166107171264</v>
       </c>
       <c r="BQ6" t="n">
         <v>0</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0005371190567004886</v>
+        <v>-0.001110134990669509</v>
       </c>
       <c r="BS6" t="n">
-        <v>-0.000260605425041141</v>
+        <v>-0.00109615039568681</v>
       </c>
       <c r="BT6" t="n">
-        <v>0.0004417427308338856</v>
+        <v>-0.001320460278446708</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0002166689326361493</v>
+        <v>-0.0008014683237465098</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.0001845989056965592</v>
+        <v>-0.0004735395595802077</v>
       </c>
       <c r="BW6" t="n">
-        <v>-2.220248667851033e-05</v>
+        <v>-5.30460560748236e-05</v>
       </c>
       <c r="BX6" t="n">
-        <v>-9.168704156479467e-05</v>
+        <v>-0.001521143971869007</v>
       </c>
       <c r="BY6" t="n">
-        <v>-0.0007662057888057239</v>
+        <v>-0.001185895277181118</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0.0008235091420761369</v>
+        <v>-0.0003211819065086469</v>
       </c>
       <c r="CA6" t="n">
-        <v>-0.0009806614759274468</v>
+        <v>-0.0009005863046005064</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0.002313926499137836</v>
+        <v>-0.0007284063699696557</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0.0004714064530782103</v>
+        <v>-0.0002661678244130189</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0.0005568304870900348</v>
+        <v>-0.001314819829957062</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.003859181766982611</v>
+        <v>-0.002524126009445382</v>
       </c>
       <c r="CF6" t="n">
-        <v>-0.0001219821318702408</v>
+        <v>-0.001292991336270655</v>
       </c>
       <c r="CG6" t="n">
-        <v>-0.0008234769378979573</v>
+        <v>-0.0004586371280673574</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0001110058626654809</v>
+        <v>-0.002340136812753111</v>
       </c>
       <c r="CI6" t="n">
-        <v>-0.0008699923249756187</v>
+        <v>-0.0006484634060654359</v>
       </c>
       <c r="CJ6" t="n">
-        <v>-2.220248667851033e-05</v>
+        <v>2.947678895166283e-05</v>
       </c>
       <c r="CK6" t="n">
-        <v>-0.0002266238360022127</v>
+        <v>-0.001017678550488965</v>
       </c>
       <c r="CL6" t="n">
-        <v>-0.002449004871105859</v>
+        <v>-0.001008010435359988</v>
       </c>
       <c r="CM6" t="n">
-        <v>-8.701946100259093e-06</v>
+        <v>0.0006751146254103197</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.0001987034930851589</v>
+        <v>0.0004496503156749459</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.000229430522616017</v>
+        <v>-0.0008803832433494723</v>
       </c>
       <c r="CP6" t="n">
-        <v>-3.113280281761554e-05</v>
+        <v>-0.0003848146292769972</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0001275699509253908</v>
+        <v>-0.001920335249480443</v>
       </c>
       <c r="CR6" t="n">
-        <v>-0.001773113600398263</v>
+        <v>-0.001521837677583729</v>
       </c>
       <c r="CS6" t="n">
-        <v>-0.003383519784260647</v>
+        <v>-0.000642452363256904</v>
       </c>
       <c r="CT6" t="n">
-        <v>-0.003346049351352038</v>
+        <v>-0.003505003032668827</v>
       </c>
       <c r="CU6" t="n">
-        <v>-8.25935189895849e-05</v>
+        <v>-0.0002873497839149447</v>
       </c>
       <c r="CV6" t="n">
-        <v>-2.340093603744597e-05</v>
+        <v>-0.0001086329101875977</v>
       </c>
       <c r="CW6" t="n">
         <v>0</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0.005932995940527255</v>
+        <v>-0.00217985760772516</v>
       </c>
       <c r="CY6" t="n">
-        <v>-0.000228885993997896</v>
+        <v>-0.001756880437043376</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.0001854134552184916</v>
+        <v>-8.846947803011206e-05</v>
       </c>
       <c r="DA6" t="n">
-        <v>3.820293398533181e-05</v>
+        <v>-0.0003181155459761498</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0007170263500671681</v>
+        <v>-3.711061094096025e-05</v>
       </c>
       <c r="DC6" t="n">
-        <v>-0.003926468883955207</v>
+        <v>-0.002299984798789989</v>
       </c>
       <c r="DD6" t="n">
-        <v>-3.220993047089449e-05</v>
+        <v>-0.0002246271011999423</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0003700803922990353</v>
+        <v>-4.478358954344559e-05</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.001215894729404113</v>
+        <v>-0.002634306586263202</v>
       </c>
       <c r="DG6" t="n">
-        <v>-0.000102020063253197</v>
+        <v>-0.0003547976189542445</v>
       </c>
       <c r="DH6" t="n">
-        <v>-0.003434851168779532</v>
+        <v>-0.002744236308658454</v>
       </c>
       <c r="DI6" t="n">
-        <v>-0.0015206159390523</v>
+        <v>-0.0007084405933964144</v>
       </c>
       <c r="DJ6" t="n">
-        <v>-0.001390684190764002</v>
+        <v>-0.0005924537432784982</v>
       </c>
       <c r="DK6" t="n">
-        <v>-0.0007926950253870579</v>
+        <v>-0.001124663162629419</v>
       </c>
       <c r="DL6" t="n">
-        <v>-8.207034337504027e-05</v>
+        <v>-0.0001110124333925461</v>
       </c>
       <c r="DM6" t="n">
-        <v>-0.001675607065322937</v>
+        <v>-0.0005865625793440409</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0.003241032139938468</v>
+        <v>-0.001669871136798634</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.003302826889347416</v>
+        <v>-0.004308213925975515</v>
       </c>
       <c r="DP6" t="n">
-        <v>-0.002954973129318991</v>
+        <v>-0.001499833688422766</v>
       </c>
       <c r="DQ6" t="n">
-        <v>3.708477675474775e-05</v>
+        <v>-5.718223083475415e-05</v>
       </c>
       <c r="DR6" t="n">
-        <v>-6.635210852257988e-05</v>
+        <v>-7.262312964428642e-05</v>
       </c>
       <c r="DS6" t="n">
-        <v>-0.000250659175399115</v>
+        <v>-5.437531858827616e-05</v>
       </c>
       <c r="DT6" t="n">
-        <v>-0.002271213939143737</v>
+        <v>-0.001386759504619833</v>
       </c>
       <c r="DU6" t="n">
-        <v>-0.001999679414857131</v>
+        <v>-0.002294248566353515</v>
       </c>
       <c r="DV6" t="n">
-        <v>-2.220248667851033e-05</v>
+        <v>0</v>
       </c>
       <c r="DW6" t="n">
-        <v>-9.086961362275992e-05</v>
+        <v>-4.915374837453079e-05</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0006537697317819363</v>
+        <v>-0.001478259437751828</v>
       </c>
       <c r="DY6" t="n">
-        <v>-0.002410519498094133</v>
+        <v>-0.0009597130644285162</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.000356613408875514</v>
+        <v>-0.0003510140405616452</v>
       </c>
       <c r="EA6" t="n">
-        <v>-0.002460767104205328</v>
+        <v>-0.0003787896126458051</v>
       </c>
       <c r="EB6" t="n">
-        <v>-0.003084246448422737</v>
+        <v>-0.003996605624841046</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0.001121683794595849</v>
+        <v>-0.0006091201628834614</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0.000525277115628145</v>
+        <v>-0.0007163152390662536</v>
       </c>
       <c r="EE6" t="n">
-        <v>3.790867447077129e-05</v>
+        <v>3.743774671081945e-05</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0.001100360156664723</v>
+        <v>-0.001440672552558509</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.0009751968234574137</v>
+        <v>-0.0004867532313930889</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0.0002579577992504966</v>
+        <v>-0.0002768563377931854</v>
       </c>
       <c r="EI6" t="n">
-        <v>-0.0003922395508355936</v>
+        <v>-0.001679163074446408</v>
       </c>
       <c r="EJ6" t="n">
-        <v>-0.0008665533083247829</v>
+        <v>-0.001091396506965836</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0.0007873982478122488</v>
+        <v>2.350360388589379e-05</v>
       </c>
       <c r="EL6" t="n">
-        <v>-4.423473901503939e-05</v>
+        <v>-0.0001138044110723269</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0.0001331754957087872</v>
+        <v>7.400828892833999e-06</v>
       </c>
       <c r="EN6" t="n">
-        <v>-0.0002662596058001177</v>
+        <v>-0.0001516019952084585</v>
       </c>
       <c r="EO6" t="n">
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.0003005971082288366</v>
+        <v>-4.431314623338789e-05</v>
       </c>
       <c r="EQ6" t="n">
-        <v>-0.0005398916681027433</v>
+        <v>-0.0008890737220446893</v>
       </c>
       <c r="ER6" t="n">
-        <v>-6.660746003553099e-05</v>
+        <v>-2.211736950753218e-05</v>
       </c>
       <c r="ES6" t="n">
-        <v>-2.967626072716001e-05</v>
+        <v>-0.0002254104222848885</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0.001456203559346317</v>
+        <v>-0.0007164765172586268</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0.001069711458123909</v>
+        <v>-0.002055261841387848</v>
       </c>
       <c r="EV6" t="n">
-        <v>-0.0001376413449576758</v>
+        <v>-0.0002185911782757261</v>
       </c>
       <c r="EW6" t="n">
-        <v>-0.000932337452192658</v>
+        <v>-0.001291326724732467</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0.0003697293483481662</v>
+        <v>-0.0007430064159092836</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.0002574102964118918</v>
+        <v>7.202535292419321e-06</v>
       </c>
     </row>
     <row r="7">
@@ -3552,466 +3552,466 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0006854948361887825</v>
+        <v>0.0009400240115955971</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0003948857138032392</v>
+        <v>0.0004549260622110196</v>
       </c>
       <c r="D7" t="n">
-        <v>0.000741795290650643</v>
+        <v>-0.0005328158754372813</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0005663526623107319</v>
+        <v>5.511725525536029e-05</v>
       </c>
       <c r="F7" t="n">
-        <v>-8.87924247752414e-05</v>
+        <v>0.0002259478921437963</v>
       </c>
       <c r="G7" t="n">
-        <v>0.002688405080148837</v>
+        <v>0.0005371684497735063</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0006935775758676265</v>
+        <v>-0.0006345860192176699</v>
       </c>
       <c r="I7" t="n">
-        <v>2.981902252054414e-05</v>
+        <v>0.0005759418002268535</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0008689638235708342</v>
+        <v>-6.220467043397402e-05</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0001163384991576033</v>
+        <v>0.0002326451309089761</v>
       </c>
       <c r="L7" t="n">
-        <v>-7.640586797066362e-05</v>
+        <v>2.754614249723675e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.0005209541715001931</v>
+        <v>-0.000115474328417231</v>
       </c>
       <c r="N7" t="n">
-        <v>0.000857057526632049</v>
+        <v>0.0001642557271298251</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0008714160675827809</v>
+        <v>-0.0005104693403802596</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0005297633314945704</v>
+        <v>-0.0003856640864927707</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.00510580872673107</v>
+        <v>0.003547045068965826</v>
       </c>
       <c r="R7" t="n">
-        <v>0.0005888813946735072</v>
+        <v>-0.0001050908897513247</v>
       </c>
       <c r="S7" t="n">
-        <v>-4.413913392039556e-05</v>
+        <v>-0.0007968070569204011</v>
       </c>
       <c r="T7" t="n">
-        <v>-7.386427516845596e-05</v>
+        <v>1.303349096508088e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0007895021857004025</v>
+        <v>0.0006632967951581082</v>
       </c>
       <c r="V7" t="n">
-        <v>0.000458033653860862</v>
+        <v>-0.0001768852764389983</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0006079603542121226</v>
+        <v>0.001345757105888934</v>
       </c>
       <c r="X7" t="n">
-        <v>0.0003509783120920207</v>
+        <v>0.001902574637765397</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0001889651297038164</v>
+        <v>7.393392939183951e-05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.001867828908639802</v>
+        <v>0.001435298975014032</v>
       </c>
       <c r="AA7" t="n">
-        <v>0.002731035482245165</v>
+        <v>0.0008167747494587374</v>
       </c>
       <c r="AB7" t="n">
-        <v>9.291426252564514e-05</v>
+        <v>-0.0008891463230432328</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.001009361839091322</v>
+        <v>-0.00108475981739658</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.004494362522864948</v>
+        <v>0.00486398431497404</v>
       </c>
       <c r="AE7" t="n">
-        <v>0.005905146550689616</v>
+        <v>0.004595641296916209</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.001076072635459518</v>
+        <v>0.001516682792037433</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0009423740030285511</v>
+        <v>1.46665674093771e-05</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.0001159681782358313</v>
+        <v>0.0006328682077474168</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.0006743994483868366</v>
+        <v>0.00039321977691123</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.004063194085802097</v>
+        <v>0.003254585131706628</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.01147903057288314</v>
+        <v>0.01822156180728539</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0003406321416354163</v>
+        <v>-0.0005475967721534358</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.004284984838389644</v>
+        <v>4.461923664549338e-05</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.000249895214303214</v>
+        <v>-0.0009199569316665213</v>
       </c>
       <c r="AO7" t="n">
-        <v>5.756713394643458e-05</v>
+        <v>0.001043070327944307</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0001031796255461293</v>
+        <v>-2.523948796360201e-05</v>
       </c>
       <c r="AQ7" t="n">
-        <v>-0.0002647287492499151</v>
+        <v>0.002074303755874462</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.00783174369810829</v>
+        <v>0.006158812969948657</v>
       </c>
       <c r="AS7" t="n">
-        <v>-0.001215299967582056</v>
+        <v>0.0002946547784320797</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0.001095685924352252</v>
+        <v>2.923600707682158e-05</v>
       </c>
       <c r="AU7" t="n">
-        <v>-0.0005040024061458038</v>
+        <v>0.000737287237281975</v>
       </c>
       <c r="AV7" t="n">
-        <v>-0.0002219024306202244</v>
+        <v>-0.001168442139984477</v>
       </c>
       <c r="AW7" t="n">
-        <v>-0.0007136754386694478</v>
+        <v>-0.0004760992856191359</v>
       </c>
       <c r="AX7" t="n">
-        <v>-4.123227575040245e-05</v>
+        <v>-0.000376130473373032</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.001046294100500345</v>
+        <v>1.915623708247382e-05</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.001905852108162026</v>
+        <v>7.37071822805635e-05</v>
       </c>
       <c r="BA7" t="n">
-        <v>0.00287715041089463</v>
+        <v>0.000443392819728311</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.003181843894052005</v>
+        <v>0.001049938213463963</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0002749830397736575</v>
+        <v>4.434797334504359e-05</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.000134577423549026</v>
+        <v>5.89448865310982e-05</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.001254833478314066</v>
+        <v>-2.953787941846198e-05</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.002980537150429003</v>
+        <v>0.0003845064029741552</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0005004802543070563</v>
+        <v>-0.0004279076611374388</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0003079961546759879</v>
+        <v>-7.921275775807368e-05</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.004895607902468829</v>
+        <v>0.003369476241020608</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0006497540032869454</v>
+        <v>-8.852174950899072e-05</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0002497268430062872</v>
+        <v>9.199959116956702e-05</v>
       </c>
       <c r="BL7" t="n">
-        <v>-1.654086121360421e-05</v>
+        <v>0.000317960579375709</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.000933137703635567</v>
+        <v>0.0001560062402495788</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.001551458018687862</v>
+        <v>0.0002072232089993797</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0001430311785879545</v>
+        <v>0.0003732436063866529</v>
       </c>
       <c r="BP7" t="n">
-        <v>-0.0009703432372793752</v>
+        <v>-0.0006225061223843975</v>
       </c>
       <c r="BQ7" t="n">
         <v>0</v>
       </c>
       <c r="BR7" t="n">
-        <v>0.0009440585165130744</v>
+        <v>0.0008977504909314037</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0006648829599613937</v>
+        <v>-0.0001872112655352199</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0007112791092975467</v>
+        <v>0.0006014603271368769</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0008983420489617422</v>
+        <v>0.0001914744118812816</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.001288081363396604</v>
+        <v>0.0001966098884556122</v>
       </c>
       <c r="BW7" t="n">
         <v>0</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0004863301409932297</v>
+        <v>-0.0005466213829793787</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.001500927991117707</v>
+        <v>0.0005930650760915812</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.0004725359829399756</v>
+        <v>0.0004728321377836852</v>
       </c>
       <c r="CA7" t="n">
-        <v>-0.0003968686498073582</v>
+        <v>-0.0005896382056704008</v>
       </c>
       <c r="CB7" t="n">
-        <v>-8.924035122324648e-05</v>
+        <v>0.0003352824954596989</v>
       </c>
       <c r="CC7" t="n">
-        <v>0.0003394727637281103</v>
+        <v>0.0007440319028585218</v>
       </c>
       <c r="CD7" t="n">
-        <v>-0.0002018497610320247</v>
+        <v>0.0002638276057272238</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.0007670752408735215</v>
+        <v>-5.446998876800223e-05</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.000649833347205836</v>
+        <v>-0.0006017123356018284</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0001183033957682544</v>
+        <v>-0.0002055930553491847</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0006525906543578374</v>
+        <v>-0.0006673128783342419</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.0001922685060076868</v>
+        <v>9.590316169039213e-07</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0</v>
+        <v>4.648242164404515e-05</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.000623712449488567</v>
+        <v>6.054810761629283e-05</v>
       </c>
       <c r="CL7" t="n">
-        <v>-0.0004739791840860042</v>
+        <v>-0.0007565402036556813</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0006263716201810599</v>
+        <v>0.001181767347027396</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.001335507521060469</v>
+        <v>0.0006820215633565663</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0006402801117164014</v>
+        <v>0.0008691088851061846</v>
       </c>
       <c r="CP7" t="n">
-        <v>8.860049680126659e-05</v>
+        <v>-0.0001984369678177944</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.001590024921809374</v>
+        <v>0.001062731437417752</v>
       </c>
       <c r="CR7" t="n">
-        <v>-0.0002027737440924826</v>
+        <v>0.0006534801275446201</v>
       </c>
       <c r="CS7" t="n">
-        <v>-0.0008466563921320335</v>
+        <v>-0.0003914116469671547</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0.001330471759027502</v>
+        <v>-0.0003249905996077107</v>
       </c>
       <c r="CU7" t="n">
-        <v>-3.120124804992796e-05</v>
+        <v>1.384262616873077e-05</v>
       </c>
       <c r="CV7" t="n">
-        <v>4.437436431580788e-05</v>
+        <v>-7.378558949895364e-05</v>
       </c>
       <c r="CW7" t="n">
         <v>0</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0.0006980546384927289</v>
+        <v>-0.00145073274673998</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0009687834946160434</v>
+        <v>0.0005899529649008028</v>
       </c>
       <c r="CZ7" t="n">
-        <v>4.599132216033807e-05</v>
+        <v>8.861363825532487e-05</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0002969594183328261</v>
+        <v>0.0001048231728024152</v>
       </c>
       <c r="DB7" t="n">
-        <v>0.001440466172853777</v>
+        <v>0.000564003319199563</v>
       </c>
       <c r="DC7" t="n">
-        <v>-0.001173879734882305</v>
+        <v>-0.0003266463298947808</v>
       </c>
       <c r="DD7" t="n">
-        <v>0.0001660524101367633</v>
+        <v>-0.0001024912493335861</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.001212327922529394</v>
+        <v>0.001605126656068484</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0003593619144326599</v>
+        <v>3.181725514082021e-05</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0005033272204682138</v>
+        <v>-2.91938263720648e-05</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0.0007547662739824934</v>
+        <v>-0.0006861536761690269</v>
       </c>
       <c r="DI7" t="n">
-        <v>-0.0003404160635920028</v>
+        <v>-0.0003529953428994314</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0002959586874736131</v>
+        <v>9.394597031135986e-05</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0006955596428398104</v>
+        <v>-0.0002596311129474116</v>
       </c>
       <c r="DL7" t="n">
-        <v>2.95465707906839e-05</v>
+        <v>8.845209528557385e-05</v>
       </c>
       <c r="DM7" t="n">
-        <v>-0.0009579355651290421</v>
+        <v>-8.917725520857239e-05</v>
       </c>
       <c r="DN7" t="n">
-        <v>-0.001022730683467854</v>
+        <v>-0.000323499159739693</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.0005055020746613015</v>
+        <v>-0.002479287518729978</v>
       </c>
       <c r="DP7" t="n">
-        <v>-0.001140322973084668</v>
+        <v>-0.0004293705119493342</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0003165890032006513</v>
+        <v>6.088023600349102e-05</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.708134761398312e-05</v>
+        <v>5.449519613232028e-07</v>
       </c>
       <c r="DS7" t="n">
         <v>0</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.0006159409491451717</v>
+        <v>-0.0004466110697603831</v>
       </c>
       <c r="DU7" t="n">
-        <v>-0.0004773942414567856</v>
+        <v>-0.001292540182159663</v>
       </c>
       <c r="DV7" t="n">
         <v>0</v>
       </c>
       <c r="DW7" t="n">
-        <v>4.556845205132e-05</v>
+        <v>0.0001180290815089247</v>
       </c>
       <c r="DX7" t="n">
-        <v>0.0001728880676200584</v>
+        <v>0.0003860877667546447</v>
       </c>
       <c r="DY7" t="n">
-        <v>-0.001250787731289915</v>
+        <v>0.000150034775813762</v>
       </c>
       <c r="DZ7" t="n">
-        <v>-8.643042350906516e-05</v>
+        <v>0.0001041046995836015</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0001809196412078551</v>
+        <v>0.0001502561324946528</v>
       </c>
       <c r="EB7" t="n">
-        <v>-0.0002929956278710954</v>
+        <v>-0.000281769465701881</v>
       </c>
       <c r="EC7" t="n">
-        <v>-0.0002355371240473025</v>
+        <v>-2.798542873572169e-06</v>
       </c>
       <c r="ED7" t="n">
-        <v>0.0001032711358157412</v>
+        <v>-2.969928319392912e-05</v>
       </c>
       <c r="EE7" t="n">
-        <v>5.896226927557535e-05</v>
+        <v>0.0001062138389145428</v>
       </c>
       <c r="EF7" t="n">
-        <v>-0.0005059837788598976</v>
+        <v>-0.0005180229786209967</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0006932812947259448</v>
+        <v>1.560062402494733e-05</v>
       </c>
       <c r="EH7" t="n">
-        <v>8.018869237813031e-05</v>
+        <v>-7.398638650491507e-05</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0001993852682446673</v>
+        <v>-0.0006709801524220127</v>
       </c>
       <c r="EJ7" t="n">
-        <v>-0.0004204924939734233</v>
+        <v>-0.0004287471595648574</v>
       </c>
       <c r="EK7" t="n">
-        <v>-0.000277936178571847</v>
+        <v>0.0009821929788201955</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
       </c>
       <c r="EM7" t="n">
-        <v>1.474491300499925e-05</v>
+        <v>5.98092889232682e-05</v>
       </c>
       <c r="EN7" t="n">
-        <v>-7.75695549601274e-05</v>
+        <v>-0.0001171086821014133</v>
       </c>
       <c r="EO7" t="n">
         <v>0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.0001460897603694722</v>
+        <v>0.0001378337460484991</v>
       </c>
       <c r="EQ7" t="n">
-        <v>-1.566906925729583e-05</v>
+        <v>-0.0002107188667831605</v>
       </c>
       <c r="ER7" t="n">
         <v>0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0</v>
+        <v>-3.965872008293569e-07</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.0009982259739961473</v>
+        <v>-0.0003750919188912738</v>
       </c>
       <c r="EU7" t="n">
-        <v>-0.0002636126759457791</v>
+        <v>-0.0008280604689339166</v>
       </c>
       <c r="EV7" t="n">
-        <v>0</v>
+        <v>-5.908076483883695e-05</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0.000295573881387573</v>
+        <v>-0.0001824500458700085</v>
       </c>
       <c r="EX7" t="n">
-        <v>-0.0002789400813259235</v>
+        <v>-0.0002600763423046826</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0001621920112786279</v>
+        <v>2.95465707906617e-05</v>
       </c>
     </row>
     <row r="8">
@@ -4021,466 +4021,466 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.001675643354704129</v>
+        <v>0.002455145869879141</v>
       </c>
       <c r="C8" t="n">
-        <v>0.00111314532678384</v>
+        <v>0.001044573506212484</v>
       </c>
       <c r="D8" t="n">
-        <v>0.00112567693156207</v>
+        <v>0.0001404397798208085</v>
       </c>
       <c r="E8" t="n">
-        <v>0.001321881158903468</v>
+        <v>0.0007108019539115662</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0006605680345228071</v>
+        <v>0.0004792720532099199</v>
       </c>
       <c r="G8" t="n">
-        <v>0.003951811015749138</v>
+        <v>0.001577630281454093</v>
       </c>
       <c r="H8" t="n">
-        <v>0.001807339709318676</v>
+        <v>0.0001841695506110102</v>
       </c>
       <c r="I8" t="n">
-        <v>0.001196258930255459</v>
+        <v>0.001656429008898702</v>
       </c>
       <c r="J8" t="n">
-        <v>0.002062145532534062</v>
+        <v>0.0009466454331930079</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0005556961463562493</v>
+        <v>0.0007096409388953007</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0005044109851474465</v>
+        <v>0.0003763851040205268</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0002226495382931542</v>
+        <v>0.0002812205467160239</v>
       </c>
       <c r="N8" t="n">
-        <v>0.002812412444032561</v>
+        <v>0.003070759531460476</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0009609265779583487</v>
+        <v>0.0005584791752016094</v>
       </c>
       <c r="P8" t="n">
-        <v>0.001061996421000167</v>
+        <v>0.0004561349993957436</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.01235855321369627</v>
+        <v>0.008490570253903909</v>
       </c>
       <c r="R8" t="n">
-        <v>0.001952375061363865</v>
+        <v>0.0009206353541417801</v>
       </c>
       <c r="S8" t="n">
-        <v>0.001569307047563129</v>
+        <v>0.001032338960993481</v>
       </c>
       <c r="T8" t="n">
-        <v>0.0004613437154572714</v>
+        <v>0.0006998773648399847</v>
       </c>
       <c r="U8" t="n">
-        <v>0.001900227500769963</v>
+        <v>0.001260692039459932</v>
       </c>
       <c r="V8" t="n">
-        <v>0.002132065143373957</v>
+        <v>0.002428811099947348</v>
       </c>
       <c r="W8" t="n">
-        <v>0.001750107040397883</v>
+        <v>0.002148359700248209</v>
       </c>
       <c r="X8" t="n">
-        <v>0.002477809548331111</v>
+        <v>0.004068014382664087</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.0006953015475285373</v>
+        <v>0.0003177462738878811</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.003901014799089092</v>
+        <v>0.003264742001947002</v>
       </c>
       <c r="AA8" t="n">
-        <v>0.005013258805643123</v>
+        <v>0.003676365811259777</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.0004259523409001154</v>
+        <v>0.0007270996896005826</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.002743377094725022</v>
+        <v>-0.0002507329395007391</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.008253184693189239</v>
+        <v>0.006919986910343947</v>
       </c>
       <c r="AE8" t="n">
-        <v>0.008599646049985586</v>
+        <v>0.00607631377463502</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.00250459764738589</v>
+        <v>0.003421089139467428</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.001204166355148964</v>
+        <v>0.000749847320339872</v>
       </c>
       <c r="AH8" t="n">
-        <v>0.0008671671006489856</v>
+        <v>0.001027700955734265</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.00131282189551275</v>
+        <v>0.002056074382009729</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.006678258315860277</v>
+        <v>0.003962765002780791</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.01991720302382423</v>
+        <v>0.02203712158059989</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.001108898288515775</v>
+        <v>-7.318438159197859e-05</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.007594478751350578</v>
+        <v>0.0037663052443034</v>
       </c>
       <c r="AN8" t="n">
-        <v>0.002666924964484107</v>
+        <v>0.001826151049804206</v>
       </c>
       <c r="AO8" t="n">
-        <v>0.003584199492623435</v>
+        <v>0.002193792904757627</v>
       </c>
       <c r="AP8" t="n">
-        <v>0.001828914007072963</v>
+        <v>0.0008497595331254382</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.001486460640109458</v>
+        <v>0.004007590423161103</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.009574235495015041</v>
+        <v>0.007215119487898225</v>
       </c>
       <c r="AS8" t="n">
-        <v>0.0001628029311217943</v>
+        <v>0.002488105877994143</v>
       </c>
       <c r="AT8" t="n">
-        <v>0.001255630618367226</v>
+        <v>0.001250422375277607</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.001195318150203808</v>
+        <v>0.001841779418303122</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.0002220150686195632</v>
+        <v>0.0003094079514502218</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.001109324518909549</v>
+        <v>0.0007146746421409583</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0006657987928743892</v>
+        <v>0.0003384595153920811</v>
       </c>
       <c r="AY8" t="n">
-        <v>0.00251765360300768</v>
+        <v>0.0009436135927151341</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.002483873819785787</v>
+        <v>0.0008570617984134304</v>
       </c>
       <c r="BA8" t="n">
-        <v>0.00605764017220905</v>
+        <v>0.001851031718735493</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.004889682829114964</v>
+        <v>0.003975461302406396</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0007287205012991155</v>
+        <v>0.0002491535254639299</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0003612410056094334</v>
+        <v>0.0003338789712993756</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.001990525962581</v>
+        <v>0.0003632840147256594</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.005459592170029698</v>
+        <v>0.002335737679859035</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.001609696042029357</v>
+        <v>0.001231982987517163</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0008870511736191244</v>
+        <v>0.0007907612326783415</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.009493499029113603</v>
+        <v>0.007968063728236946</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.002714579099425007</v>
+        <v>0.0007802270518784349</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.001098429281827901</v>
+        <v>0.002637437306333448</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0004966358886135142</v>
+        <v>0.0006288603231518169</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.002002920806455205</v>
+        <v>0.0006179376357156762</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.006382943508027841</v>
+        <v>0.003076765204409526</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.001580768564030144</v>
+        <v>0.002355004714258005</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0008477096966091168</v>
+        <v>-0.0001328613099330467</v>
       </c>
       <c r="BQ8" t="n">
         <v>0</v>
       </c>
       <c r="BR8" t="n">
-        <v>0.002251019304417012</v>
+        <v>0.002219716438960281</v>
       </c>
       <c r="BS8" t="n">
-        <v>0.002292856696347156</v>
+        <v>0.0006564366323508486</v>
       </c>
       <c r="BT8" t="n">
-        <v>0.001244546635727581</v>
+        <v>0.001542921200310021</v>
       </c>
       <c r="BU8" t="n">
-        <v>0.002138692803792314</v>
+        <v>0.001650540234997047</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.002355377566777139</v>
+        <v>0.0003357628010476704</v>
       </c>
       <c r="BW8" t="n">
-        <v>2.967626072715446e-05</v>
+        <v>2.211736950751553e-05</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.00136908325741954</v>
+        <v>0.0001696191879473563</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.003141720800147099</v>
+        <v>0.001245498095785866</v>
       </c>
       <c r="BZ8" t="n">
-        <v>0.002363900495859406</v>
+        <v>0.001817081878677426</v>
       </c>
       <c r="CA8" t="n">
-        <v>0.0006728817629914702</v>
+        <v>-0.0002516130846360764</v>
       </c>
       <c r="CB8" t="n">
-        <v>0.001745905449471291</v>
+        <v>0.0009550977896687989</v>
       </c>
       <c r="CC8" t="n">
-        <v>0.001715403518341185</v>
+        <v>0.001296592907729696</v>
       </c>
       <c r="CD8" t="n">
-        <v>0.000591888901796711</v>
+        <v>0.001464014617773607</v>
       </c>
       <c r="CE8" t="n">
-        <v>7.903178485859364e-05</v>
+        <v>0.0008701589532113418</v>
       </c>
       <c r="CF8" t="n">
-        <v>0.00130852523539009</v>
+        <v>0.0002081414600133141</v>
       </c>
       <c r="CG8" t="n">
-        <v>0.0003719911740139303</v>
+        <v>0.0003168200737323601</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001321159878410141</v>
+        <v>0.0002469668960761007</v>
       </c>
       <c r="CI8" t="n">
-        <v>0.0007838351141922938</v>
+        <v>0.000216132422719012</v>
       </c>
       <c r="CJ8" t="n">
-        <v>2.292176039120075e-05</v>
+        <v>8.213878860735824e-05</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.0009752691573207545</v>
+        <v>0.0006561008261757262</v>
       </c>
       <c r="CL8" t="n">
-        <v>0.002022382543352477</v>
+        <v>0.0003103100521379909</v>
       </c>
       <c r="CM8" t="n">
-        <v>0.001090975809042893</v>
+        <v>0.001634878742958312</v>
       </c>
       <c r="CN8" t="n">
-        <v>0.001765144252408959</v>
+        <v>0.001561100456249639</v>
       </c>
       <c r="CO8" t="n">
-        <v>0.001259262565329275</v>
+        <v>0.001498651973108281</v>
       </c>
       <c r="CP8" t="n">
-        <v>0.0001930245205379516</v>
+        <v>-8.338133804156045e-05</v>
       </c>
       <c r="CQ8" t="n">
-        <v>0.003213296752539624</v>
+        <v>0.001725849641132835</v>
       </c>
       <c r="CR8" t="n">
-        <v>0.0004400169549336808</v>
+        <v>0.002156837997657818</v>
       </c>
       <c r="CS8" t="n">
-        <v>0.0006368412039852249</v>
+        <v>0.0001253183314421008</v>
       </c>
       <c r="CT8" t="n">
-        <v>0.0006776722012195452</v>
+        <v>0.0004512599366663927</v>
       </c>
       <c r="CU8" t="n">
-        <v>2.215657311669117e-05</v>
+        <v>0.0002166799315650475</v>
       </c>
       <c r="CV8" t="n">
-        <v>0.0004577740187701629</v>
+        <v>-7.80031201250697e-06</v>
       </c>
       <c r="CW8" t="n">
         <v>0</v>
       </c>
       <c r="CX8" t="n">
-        <v>0.0003471065312165705</v>
+        <v>0.0003650337660341757</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.001814887883990551</v>
+        <v>0.002795608435240962</v>
       </c>
       <c r="CZ8" t="n">
-        <v>0.0003438819975250862</v>
+        <v>0.0006407400122214913</v>
       </c>
       <c r="DA8" t="n">
-        <v>0.000601410586826237</v>
+        <v>0.0003004790797244583</v>
       </c>
       <c r="DB8" t="n">
-        <v>0.002026525981162527</v>
+        <v>0.001305309886638822</v>
       </c>
       <c r="DC8" t="n">
-        <v>0.0005372485965607493</v>
+        <v>0.0004406850507821275</v>
       </c>
       <c r="DD8" t="n">
-        <v>0.0003444329602669078</v>
+        <v>0.0001772525849335349</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.002373730867842736</v>
+        <v>0.002839828535670122</v>
       </c>
       <c r="DF8" t="n">
-        <v>0.00127849363389502</v>
+        <v>0.0005768134262317398</v>
       </c>
       <c r="DG8" t="n">
-        <v>0.001274861344365849</v>
+        <v>0.0006781134517235194</v>
       </c>
       <c r="DH8" t="n">
-        <v>-5.409205132275717e-06</v>
+        <v>0.0006560578931077365</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.0007422549958233021</v>
+        <v>0.0008049211053770904</v>
       </c>
       <c r="DJ8" t="n">
-        <v>0.0005865686144399584</v>
+        <v>0.0009345602555015541</v>
       </c>
       <c r="DK8" t="n">
-        <v>0.001691876538833068</v>
+        <v>0.0007111466101808323</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.0001868651440979613</v>
+        <v>0.0002456067643455684</v>
       </c>
       <c r="DM8" t="n">
-        <v>-0.0001919108481878179</v>
+        <v>0.0007723994073701723</v>
       </c>
       <c r="DN8" t="n">
-        <v>0.001562804609673254</v>
+        <v>0.001811514454858401</v>
       </c>
       <c r="DO8" t="n">
-        <v>0.001376070810746405</v>
+        <v>3.814567421933646e-07</v>
       </c>
       <c r="DP8" t="n">
-        <v>0.0006429715582623646</v>
+        <v>0.0005780241541574194</v>
       </c>
       <c r="DQ8" t="n">
-        <v>0.0004511738194803772</v>
+        <v>0.0002070571536217397</v>
       </c>
       <c r="DR8" t="n">
-        <v>0.0003653368628632303</v>
+        <v>0.0002154914493638443</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>2.215657311669117e-05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.001108323955808124</v>
+        <v>5.204319952693271e-05</v>
       </c>
       <c r="DU8" t="n">
-        <v>0.0008644604370639158</v>
+        <v>0.001560396536984063</v>
       </c>
       <c r="DV8" t="n">
         <v>0</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.0005805965447091221</v>
+        <v>0.0003948812682668279</v>
       </c>
       <c r="DX8" t="n">
-        <v>0.001516205097022313</v>
+        <v>0.0007884878081341002</v>
       </c>
       <c r="DY8" t="n">
-        <v>0.001392570302915014</v>
+        <v>0.001409364201538271</v>
       </c>
       <c r="DZ8" t="n">
-        <v>0.0001920498622345057</v>
+        <v>0.0006616703022466836</v>
       </c>
       <c r="EA8" t="n">
-        <v>0.001539350507286438</v>
+        <v>0.0005631415434943221</v>
       </c>
       <c r="EB8" t="n">
-        <v>0.0002807548403708171</v>
+        <v>0.0003523486212295507</v>
       </c>
       <c r="EC8" t="n">
-        <v>0.0005186458566171199</v>
+        <v>0.0004619289832262008</v>
       </c>
       <c r="ED8" t="n">
-        <v>0.0004282187877426097</v>
+        <v>0.0003192366985668993</v>
       </c>
       <c r="EE8" t="n">
-        <v>8.218837187935203e-05</v>
+        <v>0.000140723779638352</v>
       </c>
       <c r="EF8" t="n">
-        <v>-0.0001040187819187716</v>
+        <v>0.0002771953574772085</v>
       </c>
       <c r="EG8" t="n">
-        <v>0.000471802299141355</v>
+        <v>0.0001698224773343943</v>
       </c>
       <c r="EH8" t="n">
-        <v>0.0003617165586808607</v>
+        <v>0.0002744475142139297</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.0005895874984434973</v>
+        <v>-6.265506892554895e-05</v>
       </c>
       <c r="EJ8" t="n">
-        <v>-2.974419988104327e-05</v>
+        <v>0.0002731988303812216</v>
       </c>
       <c r="EK8" t="n">
-        <v>-5.908419497785978e-05</v>
+        <v>0.00148390234468076</v>
       </c>
       <c r="EL8" t="n">
         <v>0</v>
       </c>
       <c r="EM8" t="n">
-        <v>7.656559318608147e-05</v>
+        <v>0.0002685729389387631</v>
       </c>
       <c r="EN8" t="n">
-        <v>0.0003241289367671846</v>
+        <v>-4.43590597952015e-05</v>
       </c>
       <c r="EO8" t="n">
         <v>0</v>
       </c>
       <c r="EP8" t="n">
-        <v>2.903197263924851e-05</v>
+        <v>0.0003561581462219077</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0.0003325975470101078</v>
+        <v>3.524960933978527e-05</v>
       </c>
       <c r="ER8" t="n">
-        <v>2.35036038859271e-05</v>
+        <v>0</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.0001977791537144252</v>
+        <v>3.087606038843227e-05</v>
       </c>
       <c r="ET8" t="n">
-        <v>-0.0003607269844708133</v>
+        <v>0.0005102410100737808</v>
       </c>
       <c r="EU8" t="n">
-        <v>0.0003586450090049486</v>
+        <v>0.0007015202724040936</v>
       </c>
       <c r="EV8" t="n">
-        <v>0.0002285335466444216</v>
+        <v>0.000118299772724062</v>
       </c>
       <c r="EW8" t="n">
-        <v>0.0002574102964118224</v>
+        <v>0.0004141401645317205</v>
       </c>
       <c r="EX8" t="n">
-        <v>0.0004403086020043273</v>
+        <v>-0.0001000529091467445</v>
       </c>
       <c r="EY8" t="n">
-        <v>0.0004642431296658312</v>
+        <v>0.0005642010232051715</v>
       </c>
     </row>
     <row r="9">
@@ -4490,466 +4490,466 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.005502676977989241</v>
+        <v>0.003760576621748613</v>
       </c>
       <c r="C9" t="n">
-        <v>0.00245199409158049</v>
+        <v>0.002256345973049168</v>
       </c>
       <c r="D9" t="n">
-        <v>0.001568511393903493</v>
+        <v>0.0003744149765990357</v>
       </c>
       <c r="E9" t="n">
-        <v>0.002017114914425444</v>
+        <v>0.001296787503684027</v>
       </c>
       <c r="F9" t="n">
-        <v>0.002304283604135882</v>
+        <v>0.001776198934280659</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007915647921760383</v>
+        <v>0.002012429712932784</v>
       </c>
       <c r="H9" t="n">
-        <v>0.002726418050767765</v>
+        <v>0.002219591595146453</v>
       </c>
       <c r="I9" t="n">
-        <v>0.00473205891570041</v>
+        <v>0.003049141503848429</v>
       </c>
       <c r="J9" t="n">
-        <v>0.006806747558449233</v>
+        <v>0.001953818827708698</v>
       </c>
       <c r="K9" t="n">
-        <v>0.001535568787214037</v>
+        <v>0.0009779951100244099</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00109499852027225</v>
+        <v>0.0006723716381417666</v>
       </c>
       <c r="M9" t="n">
-        <v>0.002599704579025097</v>
+        <v>0.002446212791040348</v>
       </c>
       <c r="N9" t="n">
-        <v>0.01546698393813204</v>
+        <v>0.00954788816180847</v>
       </c>
       <c r="O9" t="n">
-        <v>0.004430577223088861</v>
+        <v>0.00156897572528123</v>
       </c>
       <c r="P9" t="n">
-        <v>0.001378878094641167</v>
+        <v>0.001509769094138536</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.01612135633551455</v>
+        <v>0.01305770374776921</v>
       </c>
       <c r="R9" t="n">
-        <v>0.003331350386674581</v>
+        <v>0.003817697543651899</v>
       </c>
       <c r="S9" t="n">
-        <v>0.004669839381320595</v>
+        <v>0.003597758773223214</v>
       </c>
       <c r="T9" t="n">
-        <v>0.001772616136919325</v>
+        <v>0.002215657311669228</v>
       </c>
       <c r="U9" t="n">
-        <v>0.003415857098088371</v>
+        <v>0.002457075192421543</v>
       </c>
       <c r="V9" t="n">
-        <v>0.005413444378346177</v>
+        <v>0.006518332811030991</v>
       </c>
       <c r="W9" t="n">
-        <v>0.004135893648449018</v>
+        <v>0.005073349633251812</v>
       </c>
       <c r="X9" t="n">
-        <v>0.009871513632090234</v>
+        <v>0.01278596051394544</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.001873884592504405</v>
+        <v>0.0007957559681697202</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.006749555950266428</v>
+        <v>0.006038072575847753</v>
       </c>
       <c r="AA9" t="n">
-        <v>0.02629387269482448</v>
+        <v>0.01699266503667481</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.0009177027827116824</v>
+        <v>0.001124925991711068</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.004544030084612937</v>
+        <v>0.0005651397977394779</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.01322469445314947</v>
+        <v>0.01251849659662616</v>
       </c>
       <c r="AE9" t="n">
-        <v>0.02337894110648421</v>
+        <v>0.01909577632361693</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.00660146699266505</v>
+        <v>0.004055654233274131</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.002811482687185518</v>
+        <v>0.00415806546741374</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.001769389560601553</v>
+        <v>0.004423473901503949</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.007756068679692152</v>
+        <v>0.006098283007696837</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0.008506841165972601</v>
+        <v>0.005710886377156488</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.02690834070144422</v>
+        <v>0.03202757756189278</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.008893643031784859</v>
+        <v>0.004706601466992655</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.0129982153480071</v>
+        <v>0.0164782867340869</v>
       </c>
       <c r="AN9" t="n">
-        <v>0.009168704156479236</v>
+        <v>0.007579462102689472</v>
       </c>
       <c r="AO9" t="n">
-        <v>0.01153243497336257</v>
+        <v>0.01419617674710119</v>
       </c>
       <c r="AP9" t="n">
-        <v>0.003249630723781372</v>
+        <v>0.001680920082571458</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.01091612135633547</v>
+        <v>0.006365258774539006</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.01793575252825695</v>
+        <v>0.009577632361689504</v>
       </c>
       <c r="AS9" t="n">
-        <v>0.009777499216546536</v>
+        <v>0.005298993487270564</v>
       </c>
       <c r="AT9" t="n">
-        <v>0.006581009088060164</v>
+        <v>0.003037452079032699</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.005175490779297997</v>
+        <v>0.004527966854098775</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.002308375258952311</v>
+        <v>0.001627700503107399</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.001754935756816034</v>
+        <v>0.002269378131447064</v>
       </c>
       <c r="AX9" t="n">
-        <v>0.002914931588340253</v>
+        <v>0.0007680945347119716</v>
       </c>
       <c r="AY9" t="n">
-        <v>0.007227840571088595</v>
+        <v>0.005026769779892947</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.004715590922487523</v>
+        <v>0.005515512378564657</v>
       </c>
       <c r="BA9" t="n">
-        <v>0.01754907792980367</v>
+        <v>0.01438420557818862</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.008596073765615686</v>
+        <v>0.01353807583829516</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.001213376738680061</v>
+        <v>0.001297552344441133</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0007962253022706812</v>
+        <v>0.0006510802012429373</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.003270171149144274</v>
+        <v>0.002171326591314715</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.009131469363474087</v>
+        <v>0.01873884592504465</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.003885929175806946</v>
+        <v>0.002099655280476298</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.002139364303178504</v>
+        <v>0.003124078986147904</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.02715645449137415</v>
+        <v>0.03798334324806667</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.005829863176680538</v>
+        <v>0.002193669696020006</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.006173613287370716</v>
+        <v>0.005502676977989329</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.001444149720011823</v>
+        <v>0.001122599704579064</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.003166617342408951</v>
+        <v>0.003373779224622608</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.01157049375371799</v>
+        <v>0.007677843936070161</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.009182074584769662</v>
+        <v>0.005185825410544498</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.00156897572528123</v>
+        <v>0.001679929266136127</v>
       </c>
       <c r="BQ9" t="n">
         <v>0</v>
       </c>
       <c r="BR9" t="n">
-        <v>0.009182074584769662</v>
+        <v>0.006831714196176708</v>
       </c>
       <c r="BS9" t="n">
-        <v>0.004550862581796511</v>
+        <v>0.001873884592504493</v>
       </c>
       <c r="BT9" t="n">
-        <v>0.002485942586564027</v>
+        <v>0.001843849034860256</v>
       </c>
       <c r="BU9" t="n">
-        <v>0.005233469131933555</v>
+        <v>0.002511078286558444</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.003606356968215185</v>
+        <v>0.0009453471196454899</v>
       </c>
       <c r="BW9" t="n">
-        <v>0.0001181683899556862</v>
+        <v>0.0002367564368156216</v>
       </c>
       <c r="BX9" t="n">
-        <v>0.003390838786436612</v>
+        <v>0.001189767995240953</v>
       </c>
       <c r="BY9" t="n">
-        <v>0.005353955978584147</v>
+        <v>0.004143237644273379</v>
       </c>
       <c r="BZ9" t="n">
-        <v>0.00639500297441995</v>
+        <v>0.004552002304811275</v>
       </c>
       <c r="CA9" t="n">
-        <v>0.00196567862714504</v>
+        <v>0.002567237163814162</v>
       </c>
       <c r="CB9" t="n">
-        <v>0.005640864932622991</v>
+        <v>0.002152757298731878</v>
       </c>
       <c r="CC9" t="n">
-        <v>0.005829863176680538</v>
+        <v>0.002506635210852204</v>
       </c>
       <c r="CD9" t="n">
-        <v>0.002152757298731889</v>
+        <v>0.002919492774992582</v>
       </c>
       <c r="CE9" t="n">
-        <v>0.007885085574572126</v>
+        <v>0.01057457212713934</v>
       </c>
       <c r="CF9" t="n">
-        <v>0.00264723378941103</v>
+        <v>0.0009401441554371282</v>
       </c>
       <c r="CG9" t="n">
-        <v>0.002215657311669117</v>
+        <v>0.001034158570980836</v>
       </c>
       <c r="CH9" t="n">
-        <v>0.002287684111563748</v>
+        <v>0.001506646971935088</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.002883108743340623</v>
+        <v>0.002189997040544489</v>
       </c>
       <c r="CJ9" t="n">
-        <v>0.0002496099843993571</v>
+        <v>0.0001183782184078108</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.001436430317848414</v>
+        <v>0.002047677261613667</v>
       </c>
       <c r="CL9" t="n">
-        <v>0.003666562206204938</v>
+        <v>0.001680929095354511</v>
       </c>
       <c r="CM9" t="n">
-        <v>0.006876528117359415</v>
+        <v>0.004798288508557458</v>
       </c>
       <c r="CN9" t="n">
-        <v>0.006907090464547694</v>
+        <v>0.002872860635696817</v>
       </c>
       <c r="CO9" t="n">
-        <v>0.003088923556942247</v>
+        <v>0.00635696821515892</v>
       </c>
       <c r="CP9" t="n">
-        <v>0.0008328375966685897</v>
+        <v>0.0001728608470181303</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.007487775061124713</v>
+        <v>0.007457212713936423</v>
       </c>
       <c r="CR9" t="n">
-        <v>0.002983751846381077</v>
+        <v>0.005704407951598944</v>
       </c>
       <c r="CS9" t="n">
-        <v>0.001986552567237165</v>
+        <v>0.001642178046672416</v>
       </c>
       <c r="CT9" t="n">
-        <v>0.004676039119804421</v>
+        <v>0.001497659906396209</v>
       </c>
       <c r="CU9" t="n">
-        <v>0.001558679706601473</v>
+        <v>0.00032438808611025</v>
       </c>
       <c r="CV9" t="n">
-        <v>0.0008582420834566285</v>
+        <v>0.0006543723973825632</v>
       </c>
       <c r="CW9" t="n">
         <v>0</v>
       </c>
       <c r="CX9" t="n">
-        <v>0.004400977995110045</v>
+        <v>0.003640130216040183</v>
       </c>
       <c r="CY9" t="n">
-        <v>0.002722699023379649</v>
+        <v>0.004368174726989071</v>
       </c>
       <c r="CZ9" t="n">
-        <v>0.0004164187983342948</v>
+        <v>0.002261613691931508</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.001538916839301541</v>
+        <v>0.001331754957087861</v>
       </c>
       <c r="DB9" t="n">
-        <v>0.003926234384295046</v>
+        <v>0.003588143525741006</v>
       </c>
       <c r="DC9" t="n">
-        <v>0.001033973412112255</v>
+        <v>0.001903276131045195</v>
       </c>
       <c r="DD9" t="n">
-        <v>0.0004033419763756929</v>
+        <v>0.0005897965202004806</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.005837408312958448</v>
+        <v>0.004523227383863082</v>
       </c>
       <c r="DF9" t="n">
-        <v>0.002842298288508583</v>
+        <v>0.004638109305760796</v>
       </c>
       <c r="DG9" t="n">
-        <v>0.005501222493887559</v>
+        <v>0.002042628774422739</v>
       </c>
       <c r="DH9" t="n">
-        <v>0.01253056234718826</v>
+        <v>0.01057457212713934</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.002558001189767956</v>
+        <v>0.002456348031962075</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.001447562776957156</v>
+        <v>0.002420051858254091</v>
       </c>
       <c r="DK9" t="n">
-        <v>0.003881418092909561</v>
+        <v>0.005470660146699257</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.000345721694036305</v>
+        <v>0.0006499261447562854</v>
       </c>
       <c r="DM9" t="n">
-        <v>0.001270310192023627</v>
+        <v>0.003086797066014646</v>
       </c>
       <c r="DN9" t="n">
-        <v>0.009932762836185827</v>
+        <v>0.006693154034229831</v>
       </c>
       <c r="DO9" t="n">
-        <v>0.003196211897010892</v>
+        <v>0.001248049921996841</v>
       </c>
       <c r="DP9" t="n">
-        <v>0.00216233155750547</v>
+        <v>0.002959455460195271</v>
       </c>
       <c r="DQ9" t="n">
-        <v>0.000811232449297905</v>
+        <v>0.0005305039787798172</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.0005022156573116666</v>
+        <v>0.000535395597858468</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.0001183782184078108</v>
+        <v>2.96033155713471e-05</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.006815403422982913</v>
+        <v>0.001124593074874203</v>
       </c>
       <c r="DU9" t="n">
-        <v>0.003331295843520821</v>
+        <v>0.003492157443030419</v>
       </c>
       <c r="DV9" t="n">
-        <v>5.908419497784312e-05</v>
+        <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.001506646971934999</v>
+        <v>0.001479727730097635</v>
       </c>
       <c r="DX9" t="n">
-        <v>0.001923646049126926</v>
+        <v>0.001528861154446159</v>
       </c>
       <c r="DY9" t="n">
-        <v>0.006020782396088042</v>
+        <v>0.006845965770171126</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0.0003432137285490855</v>
+        <v>0.000858496151568977</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.002865583456425391</v>
+        <v>0.0009795447997695272</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.002005640864932612</v>
+        <v>0.003995264871263615</v>
       </c>
       <c r="EC9" t="n">
-        <v>0.004951100244498796</v>
+        <v>0.001008557457212678</v>
       </c>
       <c r="ED9" t="n">
-        <v>0.003759168704156502</v>
+        <v>0.001504230648699434</v>
       </c>
       <c r="EE9" t="n">
-        <v>0.0003866745984532738</v>
+        <v>0.0002654084340901863</v>
       </c>
       <c r="EF9" t="n">
-        <v>0.0006246281975014423</v>
+        <v>0.002182247124741921</v>
       </c>
       <c r="EG9" t="n">
-        <v>0.000799289520426305</v>
+        <v>0.001356531996461174</v>
       </c>
       <c r="EH9" t="n">
-        <v>0.000710479573712286</v>
+        <v>0.0006864274570982598</v>
       </c>
       <c r="EI9" t="n">
-        <v>0.003063652587745358</v>
+        <v>0.001474491300501291</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.001152141802067941</v>
+        <v>0.001378878094641156</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.0004440497335701732</v>
+        <v>0.001742053789731035</v>
       </c>
       <c r="EL9" t="n">
+        <v>0.0001181683899556862</v>
+      </c>
+      <c r="EM9" t="n">
+        <v>0.0004584352078239151</v>
+      </c>
+      <c r="EN9" t="n">
+        <v>0.0009436744323207957</v>
+      </c>
+      <c r="EO9" t="n">
         <v>0</v>
       </c>
-      <c r="EM9" t="n">
-        <v>0.0003545051698670587</v>
-      </c>
-      <c r="EN9" t="n">
-        <v>0.0007398638650488176</v>
-      </c>
-      <c r="EO9" t="n">
-        <v>0.0001184132622853884</v>
-      </c>
       <c r="EP9" t="n">
-        <v>0.001814396192742396</v>
+        <v>0.0008424336973478774</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0.001778471138845494</v>
+        <v>0.0010904804008252</v>
       </c>
       <c r="ER9" t="n">
-        <v>0.000144050705848453</v>
+        <v>0.0001880288310874167</v>
       </c>
       <c r="ES9" t="n">
-        <v>0.0005928237129484648</v>
+        <v>8.878366380585812e-05</v>
       </c>
       <c r="ET9" t="n">
-        <v>0.0006510802012429595</v>
+        <v>0.002218380870066239</v>
       </c>
       <c r="EU9" t="n">
-        <v>0.0008257151282807018</v>
+        <v>0.00302652106084238</v>
       </c>
       <c r="EV9" t="n">
-        <v>0.0007733491969065476</v>
+        <v>0.0002071618822136689</v>
       </c>
       <c r="EW9" t="n">
-        <v>0.0007077558242406079</v>
+        <v>0.001865008880994678</v>
       </c>
       <c r="EX9" t="n">
-        <v>0.003314590115418714</v>
+        <v>0.0003256364712847737</v>
       </c>
       <c r="EY9" t="n">
-        <v>0.002475712942651187</v>
+        <v>0.00189069423929108</v>
       </c>
     </row>
   </sheetData>
